--- a/resources/excel/Planilha_template.xlsx
+++ b/resources/excel/Planilha_template.xlsx
@@ -1,13 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="27945" windowHeight="12180"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Pagina1" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Pagina2" sheetId="2" r:id="rId5"/>
+    <sheet name="Pagina1" sheetId="1" r:id="rId1"/>
+    <sheet name="Pagina2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -26,7 +42,7 @@
     <t>Topografia:_______________________________________</t>
   </si>
   <si>
-    <t>DESENHISTA:</t>
+    <t>PARC OUT:</t>
   </si>
   <si>
     <t>DATA:</t>
@@ -68,7 +84,7 @@
     <t>MUN. EST:</t>
   </si>
   <si>
-    <t>PARC. OUTORGANTE:</t>
+    <t>DESENHISTA:</t>
   </si>
   <si>
     <t>Ger. de Preparo e Plantio:______________________________</t>
@@ -77,109 +93,451 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="25">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font/>
-    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="15">
-    <border/>
+  <borders count="23">
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <right style="thin">
+      <left/>
+      <right/>
+      <top style="thin">
         <color rgb="FF000000"/>
-      </right>
+      </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -188,6 +546,9 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -196,30 +557,31 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -231,238 +593,474 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+  <cellXfs count="36">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Moeda" xfId="2" builtinId="4"/>
+    <cellStyle name="Porcentagem" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Moeda [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Hyperlink seguido" xfId="7" builtinId="9"/>
+    <cellStyle name="Observação" xfId="8" builtinId="10"/>
+    <cellStyle name="Texto de Aviso" xfId="9" builtinId="11"/>
+    <cellStyle name="Título" xfId="10" builtinId="15"/>
+    <cellStyle name="Texto Explicativo" xfId="11" builtinId="53"/>
+    <cellStyle name="Título 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Título 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Título 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Título 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Entrada" xfId="16" builtinId="20"/>
+    <cellStyle name="Saída" xfId="17" builtinId="21"/>
+    <cellStyle name="Cálculo" xfId="18" builtinId="22"/>
+    <cellStyle name="Célula de Verificação" xfId="19" builtinId="23"/>
+    <cellStyle name="Célula Vinculada" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Bom" xfId="22" builtinId="26"/>
+    <cellStyle name="Ruim" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutro" xfId="24" builtinId="28"/>
+    <cellStyle name="Ênfase 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Ênfase 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Ênfase 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Ênfase 1" xfId="28" builtinId="32"/>
+    <cellStyle name="Ênfase 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Ênfase 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Ênfase 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Ênfase 2" xfId="32" builtinId="36"/>
+    <cellStyle name="Ênfase 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Ênfase 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Ênfase 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Ênfase 3" xfId="36" builtinId="40"/>
+    <cellStyle name="Ênfase 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Ênfase 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Ênfase 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Ênfase 4" xfId="40" builtinId="44"/>
+    <cellStyle name="Ênfase 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Ênfase 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Ênfase 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Ênfase 5" xfId="44" builtinId="48"/>
+    <cellStyle name="Ênfase 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Ênfase 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Ênfase 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Ênfase 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="200025" cy="200025"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="457200" cy="200025"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="200025" cy="200025"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="457200" cy="200025"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
@@ -492,19 +1090,79 @@
         <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -516,170 +1174,198 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:K1000"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.14"/>
-    <col customWidth="1" min="2" max="2" width="10.86"/>
-    <col customWidth="1" min="3" max="5" width="10.0"/>
-    <col customWidth="1" min="6" max="7" width="12.57"/>
-    <col customWidth="1" min="8" max="8" width="18.14"/>
-    <col customWidth="1" min="9" max="9" width="24.43"/>
-    <col customWidth="1" min="10" max="10" width="17.29"/>
-    <col customWidth="1" min="11" max="11" width="35.86"/>
+    <col min="1" max="1" width="14.152380952381" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.8666666666667" style="1" customWidth="1"/>
+    <col min="3" max="5" width="10.0095238095238" style="1" customWidth="1"/>
+    <col min="6" max="7" width="12.5809523809524" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.152380952381" style="1" customWidth="1"/>
+    <col min="9" max="9" width="24.4380952380952" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.2952380952381" style="1" customWidth="1"/>
+    <col min="11" max="11" width="35.8666666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="4"/>
-    </row>
-    <row r="2" ht="18.75" customHeight="1">
+    <row r="1" ht="18.75" customHeight="1" spans="1:11">
+      <c r="A1" s="2"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="26"/>
+    </row>
+    <row r="2" ht="18.75" customHeight="1" spans="1:11">
       <c r="A2" s="5"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -688,11 +1374,11 @@
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="6"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="9"/>
-    </row>
-    <row r="3" ht="18.75" customHeight="1">
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="28"/>
+    </row>
+    <row r="3" ht="18.75" customHeight="1" spans="1:11">
       <c r="A3" s="5"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -701,11 +1387,11 @@
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="6"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="9"/>
-    </row>
-    <row r="4" ht="18.75" customHeight="1">
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="28"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1" spans="1:11">
       <c r="A4" s="5"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -714,11 +1400,11 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="6"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="9"/>
-    </row>
-    <row r="5" ht="18.75" customHeight="1">
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="28"/>
+    </row>
+    <row r="5" ht="18.75" customHeight="1" spans="1:11">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -727,11 +1413,11 @@
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="6"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="9"/>
-    </row>
-    <row r="6" ht="18.75" customHeight="1">
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="28"/>
+    </row>
+    <row r="6" ht="18.75" customHeight="1" spans="1:11">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -740,11 +1426,11 @@
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="6"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="9"/>
-    </row>
-    <row r="7" ht="18.75" customHeight="1">
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="28"/>
+    </row>
+    <row r="7" ht="18.75" customHeight="1" spans="1:11">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -753,24 +1439,24 @@
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="6"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="9"/>
-    </row>
-    <row r="8" ht="18.75" customHeight="1">
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="28"/>
+    </row>
+    <row r="8" ht="18.75" customHeight="1" spans="1:11">
       <c r="A8" s="5"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="7"/>
-      <c r="G8" s="10"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="6"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="9"/>
-    </row>
-    <row r="9" ht="18.75" customHeight="1">
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="28"/>
+    </row>
+    <row r="9" ht="18.75" customHeight="1" spans="1:11">
       <c r="A9" s="5"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -779,11 +1465,11 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="6"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="9"/>
-    </row>
-    <row r="10" ht="18.75" customHeight="1">
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="28"/>
+    </row>
+    <row r="10" ht="18.75" customHeight="1" spans="1:11">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -792,11 +1478,11 @@
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="6"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="9"/>
-    </row>
-    <row r="11" ht="18.75" customHeight="1">
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="28"/>
+    </row>
+    <row r="11" ht="18.75" customHeight="1" spans="1:11">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -805,11 +1491,11 @@
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="6"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="9"/>
-    </row>
-    <row r="12" ht="18.75" customHeight="1">
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="28"/>
+    </row>
+    <row r="12" ht="19.5" customHeight="1" spans="1:11">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -818,11 +1504,11 @@
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="6"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="9"/>
-    </row>
-    <row r="13" ht="18.75" customHeight="1">
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="28"/>
+    </row>
+    <row r="13" ht="19.5" customHeight="1" spans="1:11">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -831,11 +1517,11 @@
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="6"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="9"/>
-    </row>
-    <row r="14" ht="18.75" customHeight="1">
+      <c r="I13" s="34"/>
+      <c r="J13" s="34"/>
+      <c r="K13" s="28"/>
+    </row>
+    <row r="14" ht="19.5" customHeight="1" spans="1:11">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -844,11 +1530,11 @@
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="6"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="9"/>
-    </row>
-    <row r="15" ht="18.75" customHeight="1">
+      <c r="I14" s="34"/>
+      <c r="J14" s="34"/>
+      <c r="K14" s="28"/>
+    </row>
+    <row r="15" ht="19.5" customHeight="1" spans="1:11">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -859,9 +1545,9 @@
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
-      <c r="K15" s="11"/>
-    </row>
-    <row r="16" ht="18.75" customHeight="1">
+      <c r="K15" s="27"/>
+    </row>
+    <row r="16" ht="19.5" customHeight="1" spans="1:11">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -872,9 +1558,9 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
-      <c r="K16" s="11"/>
-    </row>
-    <row r="17" ht="18.75" customHeight="1">
+      <c r="K16" s="27"/>
+    </row>
+    <row r="17" ht="19.5" customHeight="1" spans="1:11">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -885,9 +1571,9 @@
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
-      <c r="K17" s="11"/>
-    </row>
-    <row r="18" ht="18.75" customHeight="1">
+      <c r="K17" s="27"/>
+    </row>
+    <row r="18" ht="19.5" customHeight="1" spans="1:11">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -898,9 +1584,9 @@
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
-      <c r="K18" s="11"/>
-    </row>
-    <row r="19" ht="18.75" customHeight="1">
+      <c r="K18" s="27"/>
+    </row>
+    <row r="19" ht="19.5" customHeight="1" spans="1:11">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -911,9 +1597,9 @@
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
-      <c r="K19" s="11"/>
-    </row>
-    <row r="20" ht="18.75" customHeight="1">
+      <c r="K19" s="27"/>
+    </row>
+    <row r="20" ht="19.5" customHeight="1" spans="1:11">
       <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -924,9 +1610,9 @@
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
-      <c r="K20" s="11"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
+      <c r="K20" s="27"/>
+    </row>
+    <row r="21" ht="19.5" customHeight="1" spans="1:11">
       <c r="A21" s="5"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -937,9 +1623,9 @@
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
-      <c r="K21" s="11"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
+      <c r="K21" s="27"/>
+    </row>
+    <row r="22" ht="19.5" customHeight="1" spans="1:11">
       <c r="A22" s="5"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -950,9 +1636,9 @@
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
-      <c r="K22" s="11"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
+      <c r="K22" s="27"/>
+    </row>
+    <row r="23" ht="19.5" customHeight="1" spans="1:11">
       <c r="A23" s="5"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -963,9 +1649,9 @@
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
-      <c r="K23" s="11"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
+      <c r="K23" s="27"/>
+    </row>
+    <row r="24" ht="19.5" customHeight="1" spans="1:11">
       <c r="A24" s="5"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -976,9 +1662,9 @@
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
-      <c r="K24" s="11"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
+      <c r="K24" s="27"/>
+    </row>
+    <row r="25" ht="19.5" customHeight="1" spans="1:11">
       <c r="A25" s="5"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -989,9 +1675,9 @@
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
-      <c r="K25" s="11"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
+      <c r="K25" s="27"/>
+    </row>
+    <row r="26" ht="18.75" customHeight="1" spans="1:11">
       <c r="A26" s="5"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -1002,138 +1688,138 @@
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
-      <c r="K26" s="11"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="12" t="s">
+      <c r="K26" s="27"/>
+    </row>
+    <row r="27" ht="19.5" customHeight="1" spans="1:11">
+      <c r="A27" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="12" t="s">
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="14"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="15" t="s">
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="29"/>
+    </row>
+    <row r="28" ht="19.5" customHeight="1" spans="1:11">
+      <c r="A28" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B28" s="6"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="15" t="s">
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="10" t="s">
         <v>3</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
-      <c r="H28" s="15" t="s">
+      <c r="H28" s="10" t="s">
         <v>4</v>
       </c>
       <c r="I28" s="7"/>
-      <c r="J28" s="16" t="s">
+      <c r="J28" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K28" s="17"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="15" t="s">
+      <c r="K28" s="31"/>
+    </row>
+    <row r="29" ht="19.5" customHeight="1" spans="1:11">
+      <c r="A29" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B29" s="6"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="15" t="s">
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="10" t="s">
         <v>7</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
-      <c r="H29" s="15" t="s">
+      <c r="H29" s="10" t="s">
         <v>8</v>
       </c>
       <c r="I29" s="7"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="19"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="15" t="s">
+      <c r="J29" s="12"/>
+      <c r="K29" s="31"/>
+    </row>
+    <row r="30" ht="19.5" customHeight="1" spans="1:11">
+      <c r="A30" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B30" s="6"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="15" t="s">
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
-      <c r="H30" s="15" t="s">
+      <c r="H30" s="10" t="s">
         <v>11</v>
       </c>
       <c r="I30" s="7"/>
-      <c r="J30" s="20" t="s">
+      <c r="J30" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="K30" s="19"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="21" t="s">
+      <c r="K30" s="31"/>
+    </row>
+    <row r="31" ht="18.75" customHeight="1" spans="1:11">
+      <c r="A31" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="21" t="s">
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="21" t="s">
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="I31" s="22"/>
-      <c r="J31" s="23"/>
-      <c r="K31" s="24"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="25"/>
-      <c r="B32" s="26" t="s">
+      <c r="I31" s="15"/>
+      <c r="J31" s="16"/>
+      <c r="K31" s="33"/>
+    </row>
+    <row r="32" ht="19.5" customHeight="1" spans="1:11">
+      <c r="A32" s="17"/>
+      <c r="B32" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="27"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="29" t="s">
+      <c r="C32" s="20"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="F32" s="27"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="30" t="s">
+      <c r="F32" s="20"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="I32" s="27"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="28"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="31"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="22"/>
-      <c r="K33" s="32"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="21"/>
+    </row>
+    <row r="33" ht="18.75" customHeight="1" spans="1:11">
+      <c r="A33" s="23"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="24"/>
+    </row>
+    <row r="34" ht="19.5" customHeight="1" spans="1:11">
       <c r="A34" s="7"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -1146,7 +1832,7 @@
       <c r="J34" s="6"/>
       <c r="K34" s="6"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" ht="19.5" customHeight="1" spans="1:11">
       <c r="A35" s="7"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -1159,7 +1845,7 @@
       <c r="J35" s="6"/>
       <c r="K35" s="6"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" ht="19.5" customHeight="1" spans="1:11">
       <c r="A36" s="7"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -1172,7 +1858,7 @@
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" ht="19.5" customHeight="1" spans="1:11">
       <c r="A37" s="7"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -1185,7 +1871,7 @@
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" ht="19.5" customHeight="1" spans="1:11">
       <c r="A38" s="7"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -1198,7 +1884,7 @@
       <c r="J38" s="6"/>
       <c r="K38" s="6"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" ht="15.75" customHeight="1" spans="1:11">
       <c r="A39" s="7"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1211,7 +1897,7 @@
       <c r="J39" s="6"/>
       <c r="K39" s="6"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" ht="15.75" customHeight="1" spans="1:11">
       <c r="A40" s="7"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1224,7 +1910,7 @@
       <c r="J40" s="6"/>
       <c r="K40" s="6"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" ht="15.75" customHeight="1" spans="1:11">
       <c r="A41" s="7"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1237,7 +1923,7 @@
       <c r="J41" s="6"/>
       <c r="K41" s="6"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" ht="15.75" customHeight="1" spans="1:11">
       <c r="A42" s="7"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -1250,7 +1936,7 @@
       <c r="J42" s="6"/>
       <c r="K42" s="6"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" ht="15.75" customHeight="1" spans="1:11">
       <c r="A43" s="7"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -1263,7 +1949,7 @@
       <c r="J43" s="6"/>
       <c r="K43" s="6"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" ht="15.75" customHeight="1" spans="1:11">
       <c r="A44" s="7"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -1276,7 +1962,7 @@
       <c r="J44" s="6"/>
       <c r="K44" s="6"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" ht="15.75" customHeight="1" spans="1:11">
       <c r="A45" s="7"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -1289,7 +1975,7 @@
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" ht="15.75" customHeight="1" spans="1:11">
       <c r="A46" s="7"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -1302,7 +1988,7 @@
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" ht="15.75" customHeight="1" spans="1:11">
       <c r="A47" s="7"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -1315,7 +2001,7 @@
       <c r="J47" s="6"/>
       <c r="K47" s="6"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" ht="15.75" customHeight="1" spans="1:11">
       <c r="A48" s="7"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -1328,7 +2014,7 @@
       <c r="J48" s="6"/>
       <c r="K48" s="6"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" ht="15.75" customHeight="1" spans="1:11">
       <c r="A49" s="7"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -1341,7 +2027,7 @@
       <c r="J49" s="6"/>
       <c r="K49" s="6"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" ht="15.75" customHeight="1" spans="1:11">
       <c r="A50" s="7"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -1354,7 +2040,7 @@
       <c r="J50" s="6"/>
       <c r="K50" s="6"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" ht="15.75" customHeight="1" spans="1:11">
       <c r="A51" s="7"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -1367,7 +2053,7 @@
       <c r="J51" s="6"/>
       <c r="K51" s="6"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" ht="15.75" customHeight="1" spans="1:11">
       <c r="A52" s="7"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -1380,7 +2066,7 @@
       <c r="J52" s="6"/>
       <c r="K52" s="6"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" ht="15.75" customHeight="1" spans="1:11">
       <c r="A53" s="7"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -1393,7 +2079,7 @@
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" ht="15.75" customHeight="1" spans="1:11">
       <c r="A54" s="7"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -1406,7 +2092,7 @@
       <c r="J54" s="6"/>
       <c r="K54" s="6"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" ht="15.75" customHeight="1" spans="1:11">
       <c r="A55" s="7"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -1419,7 +2105,7 @@
       <c r="J55" s="6"/>
       <c r="K55" s="6"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" ht="15.75" customHeight="1" spans="1:11">
       <c r="A56" s="7"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -1432,7 +2118,7 @@
       <c r="J56" s="6"/>
       <c r="K56" s="6"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" ht="15.75" customHeight="1" spans="1:11">
       <c r="A57" s="7"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -1445,7 +2131,7 @@
       <c r="J57" s="6"/>
       <c r="K57" s="6"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" ht="15.75" customHeight="1" spans="1:11">
       <c r="A58" s="7"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -1458,7 +2144,7 @@
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" ht="15.75" customHeight="1" spans="1:11">
       <c r="A59" s="7"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -1471,7 +2157,7 @@
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" ht="15.75" customHeight="1" spans="1:11">
       <c r="A60" s="7"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -1484,7 +2170,7 @@
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" ht="15.75" customHeight="1" spans="1:11">
       <c r="A61" s="7"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -1497,7 +2183,7 @@
       <c r="J61" s="6"/>
       <c r="K61" s="6"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" ht="15.75" customHeight="1" spans="1:11">
       <c r="A62" s="7"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -1510,7 +2196,7 @@
       <c r="J62" s="6"/>
       <c r="K62" s="6"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" ht="15.75" customHeight="1" spans="1:11">
       <c r="A63" s="7"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -1523,7 +2209,7 @@
       <c r="J63" s="6"/>
       <c r="K63" s="6"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" ht="15.75" customHeight="1" spans="1:11">
       <c r="A64" s="7"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -1536,7 +2222,7 @@
       <c r="J64" s="6"/>
       <c r="K64" s="6"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" ht="15.75" customHeight="1" spans="1:11">
       <c r="A65" s="7"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -1549,7 +2235,7 @@
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" ht="15.75" customHeight="1" spans="1:11">
       <c r="A66" s="7"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -1562,7 +2248,7 @@
       <c r="J66" s="6"/>
       <c r="K66" s="6"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" ht="15.75" customHeight="1" spans="1:11">
       <c r="A67" s="7"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -1575,7 +2261,7 @@
       <c r="J67" s="6"/>
       <c r="K67" s="6"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" ht="15.75" customHeight="1" spans="1:11">
       <c r="A68" s="7"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -1588,7 +2274,7 @@
       <c r="J68" s="6"/>
       <c r="K68" s="6"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" ht="15.75" customHeight="1" spans="1:11">
       <c r="A69" s="7"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -1601,7 +2287,7 @@
       <c r="J69" s="6"/>
       <c r="K69" s="6"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" ht="15.75" customHeight="1" spans="1:11">
       <c r="A70" s="7"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -1614,7 +2300,7 @@
       <c r="J70" s="6"/>
       <c r="K70" s="6"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" ht="15.75" customHeight="1" spans="1:11">
       <c r="A71" s="7"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -1627,7 +2313,7 @@
       <c r="J71" s="6"/>
       <c r="K71" s="6"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" ht="15.75" customHeight="1" spans="1:11">
       <c r="A72" s="7"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -1640,7 +2326,7 @@
       <c r="J72" s="6"/>
       <c r="K72" s="6"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" ht="15.75" customHeight="1" spans="1:11">
       <c r="A73" s="7"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -1653,7 +2339,7 @@
       <c r="J73" s="6"/>
       <c r="K73" s="6"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" ht="15.75" customHeight="1" spans="1:11">
       <c r="A74" s="7"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -1666,7 +2352,7 @@
       <c r="J74" s="6"/>
       <c r="K74" s="6"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" ht="15.75" customHeight="1" spans="1:11">
       <c r="A75" s="7"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -1679,7 +2365,7 @@
       <c r="J75" s="6"/>
       <c r="K75" s="6"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" ht="15.75" customHeight="1" spans="1:11">
       <c r="A76" s="7"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -1692,7 +2378,7 @@
       <c r="J76" s="6"/>
       <c r="K76" s="6"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" ht="15.75" customHeight="1" spans="1:11">
       <c r="A77" s="7"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -1705,7 +2391,7 @@
       <c r="J77" s="6"/>
       <c r="K77" s="6"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" ht="15.75" customHeight="1" spans="1:11">
       <c r="A78" s="7"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -1718,7 +2404,7 @@
       <c r="J78" s="6"/>
       <c r="K78" s="6"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" ht="15.75" customHeight="1" spans="1:11">
       <c r="A79" s="7"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -1731,7 +2417,7 @@
       <c r="J79" s="6"/>
       <c r="K79" s="6"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" ht="15.75" customHeight="1" spans="1:11">
       <c r="A80" s="7"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -1744,7 +2430,7 @@
       <c r="J80" s="6"/>
       <c r="K80" s="6"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" ht="15.75" customHeight="1" spans="1:11">
       <c r="A81" s="7"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -1757,7 +2443,7 @@
       <c r="J81" s="6"/>
       <c r="K81" s="6"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" ht="15.75" customHeight="1" spans="1:11">
       <c r="A82" s="7"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -1770,7 +2456,7 @@
       <c r="J82" s="6"/>
       <c r="K82" s="6"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" ht="15.75" customHeight="1" spans="1:11">
       <c r="A83" s="7"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -1783,7 +2469,7 @@
       <c r="J83" s="6"/>
       <c r="K83" s="6"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" ht="15.75" customHeight="1" spans="1:11">
       <c r="A84" s="7"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -1796,7 +2482,7 @@
       <c r="J84" s="6"/>
       <c r="K84" s="6"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" ht="15.75" customHeight="1" spans="1:11">
       <c r="A85" s="7"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -1809,7 +2495,7 @@
       <c r="J85" s="6"/>
       <c r="K85" s="6"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" ht="15.75" customHeight="1" spans="1:11">
       <c r="A86" s="7"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -1822,7 +2508,7 @@
       <c r="J86" s="6"/>
       <c r="K86" s="6"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" ht="15.75" customHeight="1" spans="1:11">
       <c r="A87" s="7"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -1835,7 +2521,7 @@
       <c r="J87" s="6"/>
       <c r="K87" s="6"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" ht="15.75" customHeight="1" spans="1:11">
       <c r="A88" s="7"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -1848,7 +2534,7 @@
       <c r="J88" s="6"/>
       <c r="K88" s="6"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" ht="15.75" customHeight="1" spans="1:11">
       <c r="A89" s="7"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -1861,7 +2547,7 @@
       <c r="J89" s="6"/>
       <c r="K89" s="6"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" ht="15.75" customHeight="1" spans="1:11">
       <c r="A90" s="7"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -1874,7 +2560,7 @@
       <c r="J90" s="6"/>
       <c r="K90" s="6"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" ht="15.75" customHeight="1" spans="1:11">
       <c r="A91" s="7"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -1887,7 +2573,7 @@
       <c r="J91" s="6"/>
       <c r="K91" s="6"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" ht="15.75" customHeight="1" spans="1:11">
       <c r="A92" s="7"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -1900,7 +2586,7 @@
       <c r="J92" s="6"/>
       <c r="K92" s="6"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" ht="15.75" customHeight="1" spans="1:11">
       <c r="A93" s="7"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -1913,7 +2599,7 @@
       <c r="J93" s="6"/>
       <c r="K93" s="6"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" ht="15.75" customHeight="1" spans="1:11">
       <c r="A94" s="7"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -1926,7 +2612,7 @@
       <c r="J94" s="6"/>
       <c r="K94" s="6"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" ht="15.75" customHeight="1" spans="1:11">
       <c r="A95" s="7"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -1939,7 +2625,7 @@
       <c r="J95" s="6"/>
       <c r="K95" s="6"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" ht="15.75" customHeight="1" spans="1:11">
       <c r="A96" s="7"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -1952,7 +2638,7 @@
       <c r="J96" s="6"/>
       <c r="K96" s="6"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" ht="15.75" customHeight="1" spans="1:11">
       <c r="A97" s="7"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -1965,7 +2651,7 @@
       <c r="J97" s="6"/>
       <c r="K97" s="6"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" ht="15.75" customHeight="1" spans="1:11">
       <c r="A98" s="7"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -1978,7 +2664,7 @@
       <c r="J98" s="6"/>
       <c r="K98" s="6"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" ht="15.75" customHeight="1" spans="1:11">
       <c r="A99" s="7"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -1991,7 +2677,7 @@
       <c r="J99" s="6"/>
       <c r="K99" s="6"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" ht="15.75" customHeight="1" spans="1:11">
       <c r="A100" s="7"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -2004,7 +2690,7 @@
       <c r="J100" s="6"/>
       <c r="K100" s="6"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" ht="15.75" customHeight="1" spans="1:11">
       <c r="A101" s="7"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -2017,7 +2703,7 @@
       <c r="J101" s="6"/>
       <c r="K101" s="6"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" ht="15.75" customHeight="1" spans="1:11">
       <c r="A102" s="7"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
@@ -2030,7 +2716,7 @@
       <c r="J102" s="6"/>
       <c r="K102" s="6"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" ht="15.75" customHeight="1" spans="1:11">
       <c r="A103" s="7"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
@@ -2043,7 +2729,7 @@
       <c r="J103" s="6"/>
       <c r="K103" s="6"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" ht="15.75" customHeight="1" spans="1:11">
       <c r="A104" s="7"/>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
@@ -2056,7 +2742,7 @@
       <c r="J104" s="6"/>
       <c r="K104" s="6"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" ht="15.75" customHeight="1" spans="1:11">
       <c r="A105" s="7"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
@@ -2069,7 +2755,7 @@
       <c r="J105" s="6"/>
       <c r="K105" s="6"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" ht="15.75" customHeight="1" spans="1:11">
       <c r="A106" s="7"/>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
@@ -2082,7 +2768,7 @@
       <c r="J106" s="6"/>
       <c r="K106" s="6"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" ht="15.75" customHeight="1" spans="1:11">
       <c r="A107" s="7"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
@@ -2095,7 +2781,7 @@
       <c r="J107" s="6"/>
       <c r="K107" s="6"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" ht="15.75" customHeight="1" spans="1:11">
       <c r="A108" s="7"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
@@ -2108,7 +2794,7 @@
       <c r="J108" s="6"/>
       <c r="K108" s="6"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" ht="15.75" customHeight="1" spans="1:11">
       <c r="A109" s="7"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
@@ -2121,7 +2807,7 @@
       <c r="J109" s="6"/>
       <c r="K109" s="6"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" ht="15.75" customHeight="1" spans="1:11">
       <c r="A110" s="7"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
@@ -2134,7 +2820,7 @@
       <c r="J110" s="6"/>
       <c r="K110" s="6"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" ht="15.75" customHeight="1" spans="1:11">
       <c r="A111" s="7"/>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
@@ -2147,7 +2833,7 @@
       <c r="J111" s="6"/>
       <c r="K111" s="6"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" ht="15.75" customHeight="1" spans="1:11">
       <c r="A112" s="7"/>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
@@ -2160,7 +2846,7 @@
       <c r="J112" s="6"/>
       <c r="K112" s="6"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" ht="15.75" customHeight="1" spans="1:11">
       <c r="A113" s="7"/>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
@@ -2173,7 +2859,7 @@
       <c r="J113" s="6"/>
       <c r="K113" s="6"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" ht="15.75" customHeight="1" spans="1:11">
       <c r="A114" s="7"/>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
@@ -2186,7 +2872,7 @@
       <c r="J114" s="6"/>
       <c r="K114" s="6"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" ht="15.75" customHeight="1" spans="1:11">
       <c r="A115" s="7"/>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
@@ -2199,7 +2885,7 @@
       <c r="J115" s="6"/>
       <c r="K115" s="6"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" ht="15.75" customHeight="1" spans="1:11">
       <c r="A116" s="7"/>
       <c r="B116" s="6"/>
       <c r="C116" s="6"/>
@@ -2212,7 +2898,7 @@
       <c r="J116" s="6"/>
       <c r="K116" s="6"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" ht="15.75" customHeight="1" spans="1:11">
       <c r="A117" s="7"/>
       <c r="B117" s="6"/>
       <c r="C117" s="6"/>
@@ -2225,7 +2911,7 @@
       <c r="J117" s="6"/>
       <c r="K117" s="6"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" ht="15.75" customHeight="1" spans="1:11">
       <c r="A118" s="7"/>
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
@@ -2238,7 +2924,7 @@
       <c r="J118" s="6"/>
       <c r="K118" s="6"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" ht="15.75" customHeight="1" spans="1:11">
       <c r="A119" s="7"/>
       <c r="B119" s="6"/>
       <c r="C119" s="6"/>
@@ -2251,7 +2937,7 @@
       <c r="J119" s="6"/>
       <c r="K119" s="6"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" ht="15.75" customHeight="1" spans="1:11">
       <c r="A120" s="7"/>
       <c r="B120" s="6"/>
       <c r="C120" s="6"/>
@@ -2264,7 +2950,7 @@
       <c r="J120" s="6"/>
       <c r="K120" s="6"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" ht="15.75" customHeight="1" spans="1:11">
       <c r="A121" s="7"/>
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
@@ -2277,7 +2963,7 @@
       <c r="J121" s="6"/>
       <c r="K121" s="6"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" ht="15.75" customHeight="1" spans="1:11">
       <c r="A122" s="7"/>
       <c r="B122" s="6"/>
       <c r="C122" s="6"/>
@@ -2290,7 +2976,7 @@
       <c r="J122" s="6"/>
       <c r="K122" s="6"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" ht="15.75" customHeight="1" spans="1:11">
       <c r="A123" s="7"/>
       <c r="B123" s="6"/>
       <c r="C123" s="6"/>
@@ -2303,7 +2989,7 @@
       <c r="J123" s="6"/>
       <c r="K123" s="6"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" ht="15.75" customHeight="1" spans="1:11">
       <c r="A124" s="7"/>
       <c r="B124" s="6"/>
       <c r="C124" s="6"/>
@@ -2316,7 +3002,7 @@
       <c r="J124" s="6"/>
       <c r="K124" s="6"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" ht="15.75" customHeight="1" spans="1:11">
       <c r="A125" s="7"/>
       <c r="B125" s="6"/>
       <c r="C125" s="6"/>
@@ -2329,7 +3015,7 @@
       <c r="J125" s="6"/>
       <c r="K125" s="6"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" ht="15.75" customHeight="1" spans="1:11">
       <c r="A126" s="7"/>
       <c r="B126" s="6"/>
       <c r="C126" s="6"/>
@@ -2342,7 +3028,7 @@
       <c r="J126" s="6"/>
       <c r="K126" s="6"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" ht="15.75" customHeight="1" spans="1:11">
       <c r="A127" s="7"/>
       <c r="B127" s="6"/>
       <c r="C127" s="6"/>
@@ -2355,7 +3041,7 @@
       <c r="J127" s="6"/>
       <c r="K127" s="6"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" ht="15.75" customHeight="1" spans="1:11">
       <c r="A128" s="7"/>
       <c r="B128" s="6"/>
       <c r="C128" s="6"/>
@@ -2368,7 +3054,7 @@
       <c r="J128" s="6"/>
       <c r="K128" s="6"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" ht="15.75" customHeight="1" spans="1:11">
       <c r="A129" s="7"/>
       <c r="B129" s="6"/>
       <c r="C129" s="6"/>
@@ -2381,7 +3067,7 @@
       <c r="J129" s="6"/>
       <c r="K129" s="6"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" ht="15.75" customHeight="1" spans="1:11">
       <c r="A130" s="7"/>
       <c r="B130" s="6"/>
       <c r="C130" s="6"/>
@@ -2394,7 +3080,7 @@
       <c r="J130" s="6"/>
       <c r="K130" s="6"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" ht="15.75" customHeight="1" spans="1:11">
       <c r="A131" s="7"/>
       <c r="B131" s="6"/>
       <c r="C131" s="6"/>
@@ -2407,7 +3093,7 @@
       <c r="J131" s="6"/>
       <c r="K131" s="6"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" ht="15.75" customHeight="1" spans="1:11">
       <c r="A132" s="7"/>
       <c r="B132" s="6"/>
       <c r="C132" s="6"/>
@@ -2420,7 +3106,7 @@
       <c r="J132" s="6"/>
       <c r="K132" s="6"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" ht="15.75" customHeight="1" spans="1:11">
       <c r="A133" s="7"/>
       <c r="B133" s="6"/>
       <c r="C133" s="6"/>
@@ -2433,7 +3119,7 @@
       <c r="J133" s="6"/>
       <c r="K133" s="6"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" ht="15.75" customHeight="1" spans="1:11">
       <c r="A134" s="7"/>
       <c r="B134" s="6"/>
       <c r="C134" s="6"/>
@@ -2446,7 +3132,7 @@
       <c r="J134" s="6"/>
       <c r="K134" s="6"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" ht="15.75" customHeight="1" spans="1:11">
       <c r="A135" s="7"/>
       <c r="B135" s="6"/>
       <c r="C135" s="6"/>
@@ -2459,7 +3145,7 @@
       <c r="J135" s="6"/>
       <c r="K135" s="6"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" ht="15.75" customHeight="1" spans="1:11">
       <c r="A136" s="7"/>
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
@@ -2472,7 +3158,7 @@
       <c r="J136" s="6"/>
       <c r="K136" s="6"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" ht="15.75" customHeight="1" spans="1:11">
       <c r="A137" s="7"/>
       <c r="B137" s="6"/>
       <c r="C137" s="6"/>
@@ -2485,7 +3171,7 @@
       <c r="J137" s="6"/>
       <c r="K137" s="6"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" ht="15.75" customHeight="1" spans="1:11">
       <c r="A138" s="7"/>
       <c r="B138" s="6"/>
       <c r="C138" s="6"/>
@@ -2498,7 +3184,7 @@
       <c r="J138" s="6"/>
       <c r="K138" s="6"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" ht="15.75" customHeight="1" spans="1:11">
       <c r="A139" s="7"/>
       <c r="B139" s="6"/>
       <c r="C139" s="6"/>
@@ -2511,7 +3197,7 @@
       <c r="J139" s="6"/>
       <c r="K139" s="6"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" ht="15.75" customHeight="1" spans="1:11">
       <c r="A140" s="7"/>
       <c r="B140" s="6"/>
       <c r="C140" s="6"/>
@@ -2524,7 +3210,7 @@
       <c r="J140" s="6"/>
       <c r="K140" s="6"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" ht="15.75" customHeight="1" spans="1:11">
       <c r="A141" s="7"/>
       <c r="B141" s="6"/>
       <c r="C141" s="6"/>
@@ -2537,7 +3223,7 @@
       <c r="J141" s="6"/>
       <c r="K141" s="6"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" ht="15.75" customHeight="1" spans="1:11">
       <c r="A142" s="7"/>
       <c r="B142" s="6"/>
       <c r="C142" s="6"/>
@@ -2550,7 +3236,7 @@
       <c r="J142" s="6"/>
       <c r="K142" s="6"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" ht="15.75" customHeight="1" spans="1:11">
       <c r="A143" s="7"/>
       <c r="B143" s="6"/>
       <c r="C143" s="6"/>
@@ -2563,7 +3249,7 @@
       <c r="J143" s="6"/>
       <c r="K143" s="6"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" ht="15.75" customHeight="1" spans="1:11">
       <c r="A144" s="7"/>
       <c r="B144" s="6"/>
       <c r="C144" s="6"/>
@@ -2576,7 +3262,7 @@
       <c r="J144" s="6"/>
       <c r="K144" s="6"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" ht="15.75" customHeight="1" spans="1:11">
       <c r="A145" s="7"/>
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
@@ -2589,7 +3275,7 @@
       <c r="J145" s="6"/>
       <c r="K145" s="6"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" ht="15.75" customHeight="1" spans="1:11">
       <c r="A146" s="7"/>
       <c r="B146" s="6"/>
       <c r="C146" s="6"/>
@@ -2602,7 +3288,7 @@
       <c r="J146" s="6"/>
       <c r="K146" s="6"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" ht="15.75" customHeight="1" spans="1:11">
       <c r="A147" s="7"/>
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
@@ -2615,7 +3301,7 @@
       <c r="J147" s="6"/>
       <c r="K147" s="6"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" ht="15.75" customHeight="1" spans="1:11">
       <c r="A148" s="7"/>
       <c r="B148" s="6"/>
       <c r="C148" s="6"/>
@@ -2628,7 +3314,7 @@
       <c r="J148" s="6"/>
       <c r="K148" s="6"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" ht="15.75" customHeight="1" spans="1:11">
       <c r="A149" s="7"/>
       <c r="B149" s="6"/>
       <c r="C149" s="6"/>
@@ -2641,7 +3327,7 @@
       <c r="J149" s="6"/>
       <c r="K149" s="6"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" ht="15.75" customHeight="1" spans="1:11">
       <c r="A150" s="7"/>
       <c r="B150" s="6"/>
       <c r="C150" s="6"/>
@@ -2654,7 +3340,7 @@
       <c r="J150" s="6"/>
       <c r="K150" s="6"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" ht="15.75" customHeight="1" spans="1:11">
       <c r="A151" s="7"/>
       <c r="B151" s="6"/>
       <c r="C151" s="6"/>
@@ -2667,7 +3353,7 @@
       <c r="J151" s="6"/>
       <c r="K151" s="6"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" ht="15.75" customHeight="1" spans="1:11">
       <c r="A152" s="7"/>
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
@@ -2680,7 +3366,7 @@
       <c r="J152" s="6"/>
       <c r="K152" s="6"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" ht="15.75" customHeight="1" spans="1:11">
       <c r="A153" s="7"/>
       <c r="B153" s="6"/>
       <c r="C153" s="6"/>
@@ -2693,7 +3379,7 @@
       <c r="J153" s="6"/>
       <c r="K153" s="6"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" ht="15.75" customHeight="1" spans="1:11">
       <c r="A154" s="7"/>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
@@ -2706,7 +3392,7 @@
       <c r="J154" s="6"/>
       <c r="K154" s="6"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" ht="15.75" customHeight="1" spans="1:11">
       <c r="A155" s="7"/>
       <c r="B155" s="6"/>
       <c r="C155" s="6"/>
@@ -2719,7 +3405,7 @@
       <c r="J155" s="6"/>
       <c r="K155" s="6"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" ht="15.75" customHeight="1" spans="1:11">
       <c r="A156" s="7"/>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
@@ -2732,7 +3418,7 @@
       <c r="J156" s="6"/>
       <c r="K156" s="6"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" ht="15.75" customHeight="1" spans="1:11">
       <c r="A157" s="7"/>
       <c r="B157" s="6"/>
       <c r="C157" s="6"/>
@@ -2745,7 +3431,7 @@
       <c r="J157" s="6"/>
       <c r="K157" s="6"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" ht="15.75" customHeight="1" spans="1:11">
       <c r="A158" s="7"/>
       <c r="B158" s="6"/>
       <c r="C158" s="6"/>
@@ -2758,7 +3444,7 @@
       <c r="J158" s="6"/>
       <c r="K158" s="6"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" ht="15.75" customHeight="1" spans="1:11">
       <c r="A159" s="7"/>
       <c r="B159" s="6"/>
       <c r="C159" s="6"/>
@@ -2771,7 +3457,7 @@
       <c r="J159" s="6"/>
       <c r="K159" s="6"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" ht="15.75" customHeight="1" spans="1:11">
       <c r="A160" s="7"/>
       <c r="B160" s="6"/>
       <c r="C160" s="6"/>
@@ -2784,7 +3470,7 @@
       <c r="J160" s="6"/>
       <c r="K160" s="6"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" ht="15.75" customHeight="1" spans="1:11">
       <c r="A161" s="7"/>
       <c r="B161" s="6"/>
       <c r="C161" s="6"/>
@@ -2797,7 +3483,7 @@
       <c r="J161" s="6"/>
       <c r="K161" s="6"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" ht="15.75" customHeight="1" spans="1:11">
       <c r="A162" s="7"/>
       <c r="B162" s="6"/>
       <c r="C162" s="6"/>
@@ -2810,7 +3496,7 @@
       <c r="J162" s="6"/>
       <c r="K162" s="6"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" ht="15.75" customHeight="1" spans="1:11">
       <c r="A163" s="7"/>
       <c r="B163" s="6"/>
       <c r="C163" s="6"/>
@@ -2823,7 +3509,7 @@
       <c r="J163" s="6"/>
       <c r="K163" s="6"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" ht="15.75" customHeight="1" spans="1:11">
       <c r="A164" s="7"/>
       <c r="B164" s="6"/>
       <c r="C164" s="6"/>
@@ -2836,7 +3522,7 @@
       <c r="J164" s="6"/>
       <c r="K164" s="6"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" ht="15.75" customHeight="1" spans="1:11">
       <c r="A165" s="7"/>
       <c r="B165" s="6"/>
       <c r="C165" s="6"/>
@@ -2849,7 +3535,7 @@
       <c r="J165" s="6"/>
       <c r="K165" s="6"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" ht="15.75" customHeight="1" spans="1:11">
       <c r="A166" s="7"/>
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
@@ -2862,7 +3548,7 @@
       <c r="J166" s="6"/>
       <c r="K166" s="6"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" ht="15.75" customHeight="1" spans="1:11">
       <c r="A167" s="7"/>
       <c r="B167" s="6"/>
       <c r="C167" s="6"/>
@@ -2875,7 +3561,7 @@
       <c r="J167" s="6"/>
       <c r="K167" s="6"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" ht="15.75" customHeight="1" spans="1:11">
       <c r="A168" s="7"/>
       <c r="B168" s="6"/>
       <c r="C168" s="6"/>
@@ -2888,7 +3574,7 @@
       <c r="J168" s="6"/>
       <c r="K168" s="6"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" ht="15.75" customHeight="1" spans="1:11">
       <c r="A169" s="7"/>
       <c r="B169" s="6"/>
       <c r="C169" s="6"/>
@@ -2901,7 +3587,7 @@
       <c r="J169" s="6"/>
       <c r="K169" s="6"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" ht="15.75" customHeight="1" spans="1:11">
       <c r="A170" s="7"/>
       <c r="B170" s="6"/>
       <c r="C170" s="6"/>
@@ -2914,7 +3600,7 @@
       <c r="J170" s="6"/>
       <c r="K170" s="6"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" ht="15.75" customHeight="1" spans="1:11">
       <c r="A171" s="7"/>
       <c r="B171" s="6"/>
       <c r="C171" s="6"/>
@@ -2927,7 +3613,7 @@
       <c r="J171" s="6"/>
       <c r="K171" s="6"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" ht="15.75" customHeight="1" spans="1:11">
       <c r="A172" s="7"/>
       <c r="B172" s="6"/>
       <c r="C172" s="6"/>
@@ -2940,7 +3626,7 @@
       <c r="J172" s="6"/>
       <c r="K172" s="6"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" ht="15.75" customHeight="1" spans="1:11">
       <c r="A173" s="7"/>
       <c r="B173" s="6"/>
       <c r="C173" s="6"/>
@@ -2953,7 +3639,7 @@
       <c r="J173" s="6"/>
       <c r="K173" s="6"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" ht="15.75" customHeight="1" spans="1:11">
       <c r="A174" s="7"/>
       <c r="B174" s="6"/>
       <c r="C174" s="6"/>
@@ -2966,7 +3652,7 @@
       <c r="J174" s="6"/>
       <c r="K174" s="6"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" ht="15.75" customHeight="1" spans="1:11">
       <c r="A175" s="7"/>
       <c r="B175" s="6"/>
       <c r="C175" s="6"/>
@@ -2979,7 +3665,7 @@
       <c r="J175" s="6"/>
       <c r="K175" s="6"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" ht="15.75" customHeight="1" spans="1:11">
       <c r="A176" s="7"/>
       <c r="B176" s="6"/>
       <c r="C176" s="6"/>
@@ -2992,7 +3678,7 @@
       <c r="J176" s="6"/>
       <c r="K176" s="6"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" ht="15.75" customHeight="1" spans="1:11">
       <c r="A177" s="7"/>
       <c r="B177" s="6"/>
       <c r="C177" s="6"/>
@@ -3005,7 +3691,7 @@
       <c r="J177" s="6"/>
       <c r="K177" s="6"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" ht="15.75" customHeight="1" spans="1:11">
       <c r="A178" s="7"/>
       <c r="B178" s="6"/>
       <c r="C178" s="6"/>
@@ -3018,7 +3704,7 @@
       <c r="J178" s="6"/>
       <c r="K178" s="6"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" ht="15.75" customHeight="1" spans="1:11">
       <c r="A179" s="7"/>
       <c r="B179" s="6"/>
       <c r="C179" s="6"/>
@@ -3031,7 +3717,7 @@
       <c r="J179" s="6"/>
       <c r="K179" s="6"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" ht="15.75" customHeight="1" spans="1:11">
       <c r="A180" s="7"/>
       <c r="B180" s="6"/>
       <c r="C180" s="6"/>
@@ -3044,7 +3730,7 @@
       <c r="J180" s="6"/>
       <c r="K180" s="6"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" ht="15.75" customHeight="1" spans="1:11">
       <c r="A181" s="7"/>
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
@@ -3057,7 +3743,7 @@
       <c r="J181" s="6"/>
       <c r="K181" s="6"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" ht="15.75" customHeight="1" spans="1:11">
       <c r="A182" s="7"/>
       <c r="B182" s="6"/>
       <c r="C182" s="6"/>
@@ -3070,7 +3756,7 @@
       <c r="J182" s="6"/>
       <c r="K182" s="6"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" ht="15.75" customHeight="1" spans="1:11">
       <c r="A183" s="7"/>
       <c r="B183" s="6"/>
       <c r="C183" s="6"/>
@@ -3083,7 +3769,7 @@
       <c r="J183" s="6"/>
       <c r="K183" s="6"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" ht="15.75" customHeight="1" spans="1:11">
       <c r="A184" s="7"/>
       <c r="B184" s="6"/>
       <c r="C184" s="6"/>
@@ -3096,7 +3782,7 @@
       <c r="J184" s="6"/>
       <c r="K184" s="6"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" ht="15.75" customHeight="1" spans="1:11">
       <c r="A185" s="7"/>
       <c r="B185" s="6"/>
       <c r="C185" s="6"/>
@@ -3109,7 +3795,7 @@
       <c r="J185" s="6"/>
       <c r="K185" s="6"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" ht="15.75" customHeight="1" spans="1:11">
       <c r="A186" s="7"/>
       <c r="B186" s="6"/>
       <c r="C186" s="6"/>
@@ -3122,7 +3808,7 @@
       <c r="J186" s="6"/>
       <c r="K186" s="6"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" ht="15.75" customHeight="1" spans="1:11">
       <c r="A187" s="7"/>
       <c r="B187" s="6"/>
       <c r="C187" s="6"/>
@@ -3135,7 +3821,7 @@
       <c r="J187" s="6"/>
       <c r="K187" s="6"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" ht="15.75" customHeight="1" spans="1:11">
       <c r="A188" s="7"/>
       <c r="B188" s="6"/>
       <c r="C188" s="6"/>
@@ -3148,7 +3834,7 @@
       <c r="J188" s="6"/>
       <c r="K188" s="6"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" ht="15.75" customHeight="1" spans="1:11">
       <c r="A189" s="7"/>
       <c r="B189" s="6"/>
       <c r="C189" s="6"/>
@@ -3161,7 +3847,7 @@
       <c r="J189" s="6"/>
       <c r="K189" s="6"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" ht="15.75" customHeight="1" spans="1:11">
       <c r="A190" s="7"/>
       <c r="B190" s="6"/>
       <c r="C190" s="6"/>
@@ -3174,7 +3860,7 @@
       <c r="J190" s="6"/>
       <c r="K190" s="6"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" ht="15.75" customHeight="1" spans="1:11">
       <c r="A191" s="7"/>
       <c r="B191" s="6"/>
       <c r="C191" s="6"/>
@@ -3187,7 +3873,7 @@
       <c r="J191" s="6"/>
       <c r="K191" s="6"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" ht="15.75" customHeight="1" spans="1:11">
       <c r="A192" s="7"/>
       <c r="B192" s="6"/>
       <c r="C192" s="6"/>
@@ -3200,7 +3886,7 @@
       <c r="J192" s="6"/>
       <c r="K192" s="6"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" ht="15.75" customHeight="1" spans="1:11">
       <c r="A193" s="7"/>
       <c r="B193" s="6"/>
       <c r="C193" s="6"/>
@@ -3213,7 +3899,7 @@
       <c r="J193" s="6"/>
       <c r="K193" s="6"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" ht="15.75" customHeight="1" spans="1:11">
       <c r="A194" s="7"/>
       <c r="B194" s="6"/>
       <c r="C194" s="6"/>
@@ -3226,7 +3912,7 @@
       <c r="J194" s="6"/>
       <c r="K194" s="6"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" ht="15.75" customHeight="1" spans="1:11">
       <c r="A195" s="7"/>
       <c r="B195" s="6"/>
       <c r="C195" s="6"/>
@@ -3239,7 +3925,7 @@
       <c r="J195" s="6"/>
       <c r="K195" s="6"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" ht="15.75" customHeight="1" spans="1:11">
       <c r="A196" s="7"/>
       <c r="B196" s="6"/>
       <c r="C196" s="6"/>
@@ -3252,7 +3938,7 @@
       <c r="J196" s="6"/>
       <c r="K196" s="6"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" ht="15.75" customHeight="1" spans="1:11">
       <c r="A197" s="7"/>
       <c r="B197" s="6"/>
       <c r="C197" s="6"/>
@@ -3265,7 +3951,7 @@
       <c r="J197" s="6"/>
       <c r="K197" s="6"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" ht="15.75" customHeight="1" spans="1:11">
       <c r="A198" s="7"/>
       <c r="B198" s="6"/>
       <c r="C198" s="6"/>
@@ -3278,7 +3964,7 @@
       <c r="J198" s="6"/>
       <c r="K198" s="6"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" ht="15.75" customHeight="1" spans="1:11">
       <c r="A199" s="7"/>
       <c r="B199" s="6"/>
       <c r="C199" s="6"/>
@@ -3291,7 +3977,7 @@
       <c r="J199" s="6"/>
       <c r="K199" s="6"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" ht="15.75" customHeight="1" spans="1:11">
       <c r="A200" s="7"/>
       <c r="B200" s="6"/>
       <c r="C200" s="6"/>
@@ -3304,7 +3990,7 @@
       <c r="J200" s="6"/>
       <c r="K200" s="6"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" ht="15.75" customHeight="1" spans="1:11">
       <c r="A201" s="7"/>
       <c r="B201" s="6"/>
       <c r="C201" s="6"/>
@@ -3317,7 +4003,7 @@
       <c r="J201" s="6"/>
       <c r="K201" s="6"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" ht="15.75" customHeight="1" spans="1:11">
       <c r="A202" s="7"/>
       <c r="B202" s="6"/>
       <c r="C202" s="6"/>
@@ -3330,7 +4016,7 @@
       <c r="J202" s="6"/>
       <c r="K202" s="6"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" ht="15.75" customHeight="1" spans="1:11">
       <c r="A203" s="7"/>
       <c r="B203" s="6"/>
       <c r="C203" s="6"/>
@@ -3343,7 +4029,7 @@
       <c r="J203" s="6"/>
       <c r="K203" s="6"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" ht="15.75" customHeight="1" spans="1:11">
       <c r="A204" s="7"/>
       <c r="B204" s="6"/>
       <c r="C204" s="6"/>
@@ -3356,7 +4042,7 @@
       <c r="J204" s="6"/>
       <c r="K204" s="6"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" ht="15.75" customHeight="1" spans="1:11">
       <c r="A205" s="7"/>
       <c r="B205" s="6"/>
       <c r="C205" s="6"/>
@@ -3369,7 +4055,7 @@
       <c r="J205" s="6"/>
       <c r="K205" s="6"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" ht="15.75" customHeight="1" spans="1:11">
       <c r="A206" s="7"/>
       <c r="B206" s="6"/>
       <c r="C206" s="6"/>
@@ -3382,7 +4068,7 @@
       <c r="J206" s="6"/>
       <c r="K206" s="6"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" ht="15.75" customHeight="1" spans="1:11">
       <c r="A207" s="7"/>
       <c r="B207" s="6"/>
       <c r="C207" s="6"/>
@@ -3395,7 +4081,7 @@
       <c r="J207" s="6"/>
       <c r="K207" s="6"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" ht="15.75" customHeight="1" spans="1:11">
       <c r="A208" s="7"/>
       <c r="B208" s="6"/>
       <c r="C208" s="6"/>
@@ -3408,7 +4094,7 @@
       <c r="J208" s="6"/>
       <c r="K208" s="6"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" ht="15.75" customHeight="1" spans="1:11">
       <c r="A209" s="7"/>
       <c r="B209" s="6"/>
       <c r="C209" s="6"/>
@@ -3421,7 +4107,7 @@
       <c r="J209" s="6"/>
       <c r="K209" s="6"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" ht="15.75" customHeight="1" spans="1:11">
       <c r="A210" s="7"/>
       <c r="B210" s="6"/>
       <c r="C210" s="6"/>
@@ -3434,7 +4120,7 @@
       <c r="J210" s="6"/>
       <c r="K210" s="6"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" ht="15.75" customHeight="1" spans="1:11">
       <c r="A211" s="7"/>
       <c r="B211" s="6"/>
       <c r="C211" s="6"/>
@@ -3447,7 +4133,7 @@
       <c r="J211" s="6"/>
       <c r="K211" s="6"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" ht="15.75" customHeight="1" spans="1:11">
       <c r="A212" s="7"/>
       <c r="B212" s="6"/>
       <c r="C212" s="6"/>
@@ -3460,7 +4146,7 @@
       <c r="J212" s="6"/>
       <c r="K212" s="6"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" ht="15.75" customHeight="1" spans="1:11">
       <c r="A213" s="7"/>
       <c r="B213" s="6"/>
       <c r="C213" s="6"/>
@@ -3473,7 +4159,7 @@
       <c r="J213" s="6"/>
       <c r="K213" s="6"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" ht="15.75" customHeight="1" spans="1:11">
       <c r="A214" s="7"/>
       <c r="B214" s="6"/>
       <c r="C214" s="6"/>
@@ -3486,7 +4172,7 @@
       <c r="J214" s="6"/>
       <c r="K214" s="6"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" ht="15.75" customHeight="1" spans="1:11">
       <c r="A215" s="7"/>
       <c r="B215" s="6"/>
       <c r="C215" s="6"/>
@@ -3499,7 +4185,7 @@
       <c r="J215" s="6"/>
       <c r="K215" s="6"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" ht="15.75" customHeight="1" spans="1:11">
       <c r="A216" s="7"/>
       <c r="B216" s="6"/>
       <c r="C216" s="6"/>
@@ -3512,7 +4198,7 @@
       <c r="J216" s="6"/>
       <c r="K216" s="6"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" ht="15.75" customHeight="1" spans="1:11">
       <c r="A217" s="7"/>
       <c r="B217" s="6"/>
       <c r="C217" s="6"/>
@@ -3525,7 +4211,7 @@
       <c r="J217" s="6"/>
       <c r="K217" s="6"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" ht="15.75" customHeight="1" spans="1:11">
       <c r="A218" s="7"/>
       <c r="B218" s="6"/>
       <c r="C218" s="6"/>
@@ -3538,7 +4224,7 @@
       <c r="J218" s="6"/>
       <c r="K218" s="6"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" ht="15.75" customHeight="1" spans="1:11">
       <c r="A219" s="7"/>
       <c r="B219" s="6"/>
       <c r="C219" s="6"/>
@@ -3551,7 +4237,7 @@
       <c r="J219" s="6"/>
       <c r="K219" s="6"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" ht="15.75" customHeight="1" spans="1:11">
       <c r="A220" s="7"/>
       <c r="B220" s="7"/>
       <c r="C220" s="7"/>
@@ -3564,7 +4250,7 @@
       <c r="J220" s="7"/>
       <c r="K220" s="7"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1">
+    <row r="221" ht="15.75" customHeight="1" spans="1:11">
       <c r="A221" s="7"/>
       <c r="B221" s="7"/>
       <c r="C221" s="7"/>
@@ -3577,7 +4263,7 @@
       <c r="J221" s="7"/>
       <c r="K221" s="7"/>
     </row>
-    <row r="222" ht="15.75" customHeight="1">
+    <row r="222" ht="15.75" customHeight="1" spans="1:11">
       <c r="A222" s="7"/>
       <c r="B222" s="7"/>
       <c r="C222" s="7"/>
@@ -3590,7 +4276,7 @@
       <c r="J222" s="7"/>
       <c r="K222" s="7"/>
     </row>
-    <row r="223" ht="15.75" customHeight="1">
+    <row r="223" ht="15.75" customHeight="1" spans="1:11">
       <c r="A223" s="7"/>
       <c r="B223" s="7"/>
       <c r="C223" s="7"/>
@@ -3603,7 +4289,7 @@
       <c r="J223" s="7"/>
       <c r="K223" s="7"/>
     </row>
-    <row r="224" ht="15.75" customHeight="1">
+    <row r="224" ht="15.75" customHeight="1" spans="1:11">
       <c r="A224" s="7"/>
       <c r="B224" s="7"/>
       <c r="C224" s="7"/>
@@ -3616,7 +4302,7 @@
       <c r="J224" s="7"/>
       <c r="K224" s="7"/>
     </row>
-    <row r="225" ht="15.75" customHeight="1">
+    <row r="225" ht="15.75" customHeight="1" spans="1:11">
       <c r="A225" s="7"/>
       <c r="B225" s="7"/>
       <c r="C225" s="7"/>
@@ -3629,7 +4315,7 @@
       <c r="J225" s="7"/>
       <c r="K225" s="7"/>
     </row>
-    <row r="226" ht="15.75" customHeight="1">
+    <row r="226" ht="15.75" customHeight="1" spans="1:11">
       <c r="A226" s="7"/>
       <c r="B226" s="7"/>
       <c r="C226" s="7"/>
@@ -3642,7 +4328,7 @@
       <c r="J226" s="7"/>
       <c r="K226" s="7"/>
     </row>
-    <row r="227" ht="15.75" customHeight="1">
+    <row r="227" ht="15.75" customHeight="1" spans="1:11">
       <c r="A227" s="7"/>
       <c r="B227" s="7"/>
       <c r="C227" s="7"/>
@@ -3655,7 +4341,7 @@
       <c r="J227" s="7"/>
       <c r="K227" s="7"/>
     </row>
-    <row r="228" ht="15.75" customHeight="1">
+    <row r="228" ht="15.75" customHeight="1" spans="1:11">
       <c r="A228" s="7"/>
       <c r="B228" s="7"/>
       <c r="C228" s="7"/>
@@ -3668,7 +4354,7 @@
       <c r="J228" s="7"/>
       <c r="K228" s="7"/>
     </row>
-    <row r="229" ht="15.75" customHeight="1">
+    <row r="229" ht="15.75" customHeight="1" spans="1:11">
       <c r="A229" s="7"/>
       <c r="B229" s="7"/>
       <c r="C229" s="7"/>
@@ -3681,7 +4367,7 @@
       <c r="J229" s="7"/>
       <c r="K229" s="7"/>
     </row>
-    <row r="230" ht="15.75" customHeight="1">
+    <row r="230" ht="15.75" customHeight="1" spans="1:11">
       <c r="A230" s="7"/>
       <c r="B230" s="7"/>
       <c r="C230" s="7"/>
@@ -3694,7 +4380,7 @@
       <c r="J230" s="7"/>
       <c r="K230" s="7"/>
     </row>
-    <row r="231" ht="15.75" customHeight="1">
+    <row r="231" ht="15.75" customHeight="1" spans="1:11">
       <c r="A231" s="7"/>
       <c r="B231" s="7"/>
       <c r="C231" s="7"/>
@@ -3707,7 +4393,7 @@
       <c r="J231" s="7"/>
       <c r="K231" s="7"/>
     </row>
-    <row r="232" ht="15.75" customHeight="1">
+    <row r="232" ht="15.75" customHeight="1" spans="1:11">
       <c r="A232" s="7"/>
       <c r="B232" s="7"/>
       <c r="C232" s="7"/>
@@ -4489,211 +5175,301 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="5">
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="H27:K27"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:G32"/>
     <mergeCell ref="H32:K32"/>
-    <mergeCell ref="H27:K27"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="K28:K31"/>
-    <mergeCell ref="A27:G27"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:J1000"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.14"/>
-    <col customWidth="1" min="2" max="2" width="43.71"/>
-    <col customWidth="1" min="3" max="3" width="10.0"/>
-    <col customWidth="1" min="4" max="5" width="12.57"/>
-    <col customWidth="1" min="6" max="6" width="18.14"/>
-    <col customWidth="1" min="7" max="7" width="24.43"/>
-    <col customWidth="1" min="8" max="8" width="17.29"/>
-    <col customWidth="1" min="9" max="10" width="12.57"/>
+    <col min="1" max="1" width="14.152380952381" style="1" customWidth="1"/>
+    <col min="2" max="2" width="43.7238095238095" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.0095238095238" style="1" customWidth="1"/>
+    <col min="4" max="5" width="12.5809523809524" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.152380952381" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.4380952380952" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.2952380952381" style="1" customWidth="1"/>
+    <col min="9" max="10" width="12.5809523809524" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="4"/>
-    </row>
-    <row r="2" ht="18.75" customHeight="1">
+    <row r="1" ht="18.75" customHeight="1" spans="1:10">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="26"/>
+    </row>
+    <row r="2" ht="18.75" customHeight="1" spans="1:10">
       <c r="A2" s="5"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
       <c r="F2" s="6"/>
-      <c r="J2" s="11"/>
-    </row>
-    <row r="3" ht="18.75" customHeight="1">
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="27"/>
+    </row>
+    <row r="3" ht="18.75" customHeight="1" spans="1:10">
       <c r="A3" s="5"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
       <c r="F3" s="6"/>
-      <c r="J3" s="11"/>
-    </row>
-    <row r="4" ht="18.75" customHeight="1">
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="27"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1" spans="1:10">
       <c r="A4" s="5"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
-      <c r="J4" s="11"/>
-    </row>
-    <row r="5" ht="18.75" customHeight="1">
+      <c r="J4" s="27"/>
+    </row>
+    <row r="5" ht="18.75" customHeight="1" spans="1:10">
       <c r="A5" s="5"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
-      <c r="J5" s="11"/>
-    </row>
-    <row r="6" ht="18.75" customHeight="1">
+      <c r="J5" s="27"/>
+    </row>
+    <row r="6" ht="18.75" customHeight="1" spans="1:10">
       <c r="A6" s="5"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
       <c r="I6" s="7"/>
-      <c r="J6" s="35"/>
-    </row>
-    <row r="7" ht="18.75" customHeight="1">
+      <c r="J6" s="28"/>
+    </row>
+    <row r="7" ht="18.75" customHeight="1" spans="1:10">
       <c r="A7" s="5"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
-      <c r="J7" s="11"/>
-    </row>
-    <row r="8" ht="18.75" customHeight="1">
+      <c r="J7" s="27"/>
+    </row>
+    <row r="8" ht="18.75" customHeight="1" spans="1:10">
       <c r="A8" s="5"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
-      <c r="J8" s="11"/>
-    </row>
-    <row r="9" ht="18.75" customHeight="1">
+      <c r="J8" s="27"/>
+    </row>
+    <row r="9" ht="18.75" customHeight="1" spans="1:10">
       <c r="A9" s="5"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
-      <c r="J9" s="11"/>
-    </row>
-    <row r="10" ht="18.75" customHeight="1">
+      <c r="J9" s="27"/>
+    </row>
+    <row r="10" ht="18.75" customHeight="1" spans="1:10">
       <c r="A10" s="5"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
-      <c r="J10" s="11"/>
-    </row>
-    <row r="11" ht="18.75" customHeight="1">
+      <c r="J10" s="27"/>
+    </row>
+    <row r="11" ht="18.75" customHeight="1" spans="1:10">
       <c r="A11" s="5"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
-      <c r="J11" s="11"/>
-    </row>
-    <row r="12" ht="18.75" customHeight="1">
+      <c r="J11" s="27"/>
+    </row>
+    <row r="12" ht="18.75" customHeight="1" spans="1:10">
       <c r="A12" s="5"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
-      <c r="J12" s="11"/>
-    </row>
-    <row r="13" ht="18.75" customHeight="1">
+      <c r="J12" s="27"/>
+    </row>
+    <row r="13" ht="18.75" customHeight="1" spans="1:10">
       <c r="A13" s="5"/>
-      <c r="J13" s="11"/>
-    </row>
-    <row r="14" ht="18.75" customHeight="1">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="27"/>
+    </row>
+    <row r="14" ht="18.75" customHeight="1" spans="1:10">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
-      <c r="J14" s="11"/>
-    </row>
-    <row r="15" ht="18.75" customHeight="1">
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="27"/>
+    </row>
+    <row r="15" ht="18.75" customHeight="1" spans="1:10">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
-      <c r="J15" s="11"/>
-    </row>
-    <row r="16" ht="18.75" customHeight="1">
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="27"/>
+    </row>
+    <row r="16" ht="18.75" customHeight="1" spans="1:10">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
-      <c r="J16" s="11"/>
-    </row>
-    <row r="17" ht="18.75" customHeight="1">
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="27"/>
+    </row>
+    <row r="17" ht="18.75" customHeight="1" spans="1:10">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
-      <c r="J17" s="11"/>
-    </row>
-    <row r="18" ht="18.75" customHeight="1">
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="27"/>
+    </row>
+    <row r="18" ht="18.75" customHeight="1" spans="1:10">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
-      <c r="J18" s="11"/>
-    </row>
-    <row r="19" ht="18.75" customHeight="1">
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="27"/>
+    </row>
+    <row r="19" ht="18.75" customHeight="1" spans="1:10">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="J19" s="11"/>
-    </row>
-    <row r="20" ht="18.75" customHeight="1">
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="27"/>
+    </row>
+    <row r="20" ht="18.75" customHeight="1" spans="1:10">
       <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="J20" s="11"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="27"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" spans="1:10">
       <c r="A21" s="5"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="J21" s="11"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="27"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" spans="1:10">
       <c r="A22" s="5"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="J22" s="11"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="27"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" spans="1:10">
       <c r="A23" s="5"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -4703,9 +5479,9 @@
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
-      <c r="J23" s="11"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
+      <c r="J23" s="27"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" spans="1:10">
       <c r="A24" s="5"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -4715,9 +5491,9 @@
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
-      <c r="J24" s="11"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
+      <c r="J24" s="27"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" spans="1:10">
       <c r="A25" s="5"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -4727,9 +5503,9 @@
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
-      <c r="J25" s="11"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
+      <c r="J25" s="27"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" spans="1:10">
       <c r="A26" s="5"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -4739,129 +5515,131 @@
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
-      <c r="J26" s="11"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="12" t="s">
+      <c r="J26" s="27"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A27" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="12" t="s">
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="14"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="15" t="s">
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="29"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A28" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B28" s="6"/>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
-      <c r="F28" s="15" t="s">
+      <c r="F28" s="10" t="s">
         <v>4</v>
       </c>
       <c r="G28" s="7"/>
-      <c r="H28" s="16" t="s">
+      <c r="H28" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="I28" s="36"/>
-      <c r="J28" s="19"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="15" t="s">
+      <c r="I28" s="30"/>
+      <c r="J28" s="31"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A29" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B29" s="6"/>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
-      <c r="F29" s="15" t="s">
+      <c r="F29" s="10" t="s">
         <v>8</v>
       </c>
       <c r="G29" s="7"/>
-      <c r="H29" s="18"/>
-      <c r="J29" s="19"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="15" t="s">
+      <c r="H29" s="12"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="31"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A30" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B30" s="6"/>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="10" t="s">
         <v>10</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
-      <c r="F30" s="15" t="s">
+      <c r="F30" s="10" t="s">
         <v>11</v>
       </c>
       <c r="G30" s="7"/>
-      <c r="H30" s="20" t="s">
+      <c r="H30" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J30" s="19"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="21" t="s">
+      <c r="I30" s="30"/>
+      <c r="J30" s="31"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A31" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="21" t="s">
+      <c r="B31" s="15"/>
+      <c r="C31" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="21" t="s">
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G31" s="22"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="37"/>
-      <c r="J31" s="24"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="25"/>
-      <c r="B32" s="38" t="s">
+      <c r="G31" s="15"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="33"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A32" s="17"/>
+      <c r="B32" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="30" t="s">
+      <c r="D32" s="20"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="28"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="31"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="32"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="21"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A33" s="23"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="24"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1" spans="1:10">
       <c r="A34" s="7"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -4873,7 +5651,7 @@
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" ht="15.75" customHeight="1" spans="1:10">
       <c r="A35" s="7"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -4885,7 +5663,7 @@
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" ht="15.75" customHeight="1" spans="1:10">
       <c r="A36" s="7"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -4897,7 +5675,7 @@
       <c r="I36" s="6"/>
       <c r="J36" s="6"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" ht="15.75" customHeight="1" spans="1:10">
       <c r="A37" s="7"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -4909,7 +5687,7 @@
       <c r="I37" s="6"/>
       <c r="J37" s="6"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" ht="15.75" customHeight="1" spans="1:10">
       <c r="A38" s="7"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -4921,7 +5699,7 @@
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" ht="15.75" customHeight="1" spans="1:10">
       <c r="A39" s="7"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -4933,7 +5711,7 @@
       <c r="I39" s="6"/>
       <c r="J39" s="6"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" ht="15.75" customHeight="1" spans="1:10">
       <c r="A40" s="7"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -4945,7 +5723,7 @@
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" ht="15.75" customHeight="1" spans="1:10">
       <c r="A41" s="7"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -4957,7 +5735,7 @@
       <c r="I41" s="6"/>
       <c r="J41" s="6"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" ht="15.75" customHeight="1" spans="1:10">
       <c r="A42" s="7"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -4969,7 +5747,7 @@
       <c r="I42" s="6"/>
       <c r="J42" s="6"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" ht="15.75" customHeight="1" spans="1:10">
       <c r="A43" s="7"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -4981,7 +5759,7 @@
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" ht="15.75" customHeight="1" spans="1:10">
       <c r="A44" s="7"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -4993,7 +5771,7 @@
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" ht="15.75" customHeight="1" spans="1:10">
       <c r="A45" s="7"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -5005,7 +5783,7 @@
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" ht="15.75" customHeight="1" spans="1:10">
       <c r="A46" s="7"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -5017,7 +5795,7 @@
       <c r="I46" s="6"/>
       <c r="J46" s="6"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" ht="15.75" customHeight="1" spans="1:10">
       <c r="A47" s="7"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -5029,7 +5807,7 @@
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" ht="15.75" customHeight="1" spans="1:10">
       <c r="A48" s="7"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -5041,7 +5819,7 @@
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" ht="15.75" customHeight="1" spans="1:10">
       <c r="A49" s="7"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -5053,7 +5831,7 @@
       <c r="I49" s="6"/>
       <c r="J49" s="6"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" ht="15.75" customHeight="1" spans="1:10">
       <c r="A50" s="7"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -5065,7 +5843,7 @@
       <c r="I50" s="6"/>
       <c r="J50" s="6"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" ht="15.75" customHeight="1" spans="1:10">
       <c r="A51" s="7"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -5077,7 +5855,7 @@
       <c r="I51" s="6"/>
       <c r="J51" s="6"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" ht="15.75" customHeight="1" spans="1:10">
       <c r="A52" s="7"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -5089,7 +5867,7 @@
       <c r="I52" s="6"/>
       <c r="J52" s="6"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" ht="15.75" customHeight="1" spans="1:10">
       <c r="A53" s="7"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -5101,7 +5879,7 @@
       <c r="I53" s="6"/>
       <c r="J53" s="6"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" ht="15.75" customHeight="1" spans="1:10">
       <c r="A54" s="7"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -5113,7 +5891,7 @@
       <c r="I54" s="6"/>
       <c r="J54" s="6"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" ht="15.75" customHeight="1" spans="1:10">
       <c r="A55" s="7"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -5125,7 +5903,7 @@
       <c r="I55" s="6"/>
       <c r="J55" s="6"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" ht="15.75" customHeight="1" spans="1:10">
       <c r="A56" s="7"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -5137,7 +5915,7 @@
       <c r="I56" s="6"/>
       <c r="J56" s="6"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" ht="15.75" customHeight="1" spans="1:10">
       <c r="A57" s="7"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -5149,7 +5927,7 @@
       <c r="I57" s="6"/>
       <c r="J57" s="6"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" ht="15.75" customHeight="1" spans="1:10">
       <c r="A58" s="7"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -5161,7 +5939,7 @@
       <c r="I58" s="6"/>
       <c r="J58" s="6"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" ht="15.75" customHeight="1" spans="1:10">
       <c r="A59" s="7"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -5173,7 +5951,7 @@
       <c r="I59" s="6"/>
       <c r="J59" s="6"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" ht="15.75" customHeight="1" spans="1:10">
       <c r="A60" s="7"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -5185,7 +5963,7 @@
       <c r="I60" s="6"/>
       <c r="J60" s="6"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" ht="15.75" customHeight="1" spans="1:10">
       <c r="A61" s="7"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -5197,7 +5975,7 @@
       <c r="I61" s="6"/>
       <c r="J61" s="6"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" ht="15.75" customHeight="1" spans="1:10">
       <c r="A62" s="7"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -5209,7 +5987,7 @@
       <c r="I62" s="6"/>
       <c r="J62" s="6"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" ht="15.75" customHeight="1" spans="1:10">
       <c r="A63" s="7"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -5221,7 +5999,7 @@
       <c r="I63" s="6"/>
       <c r="J63" s="6"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" ht="15.75" customHeight="1" spans="1:10">
       <c r="A64" s="7"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -5233,7 +6011,7 @@
       <c r="I64" s="6"/>
       <c r="J64" s="6"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" ht="15.75" customHeight="1" spans="1:10">
       <c r="A65" s="7"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -5245,7 +6023,7 @@
       <c r="I65" s="6"/>
       <c r="J65" s="6"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" ht="15.75" customHeight="1" spans="1:10">
       <c r="A66" s="7"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -5257,7 +6035,7 @@
       <c r="I66" s="6"/>
       <c r="J66" s="6"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" ht="15.75" customHeight="1" spans="1:10">
       <c r="A67" s="7"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -5269,7 +6047,7 @@
       <c r="I67" s="6"/>
       <c r="J67" s="6"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" ht="15.75" customHeight="1" spans="1:10">
       <c r="A68" s="7"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -5281,7 +6059,7 @@
       <c r="I68" s="6"/>
       <c r="J68" s="6"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" ht="15.75" customHeight="1" spans="1:10">
       <c r="A69" s="7"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -5293,7 +6071,7 @@
       <c r="I69" s="6"/>
       <c r="J69" s="6"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" ht="15.75" customHeight="1" spans="1:10">
       <c r="A70" s="7"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -5305,7 +6083,7 @@
       <c r="I70" s="6"/>
       <c r="J70" s="6"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" ht="15.75" customHeight="1" spans="1:10">
       <c r="A71" s="7"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -5317,7 +6095,7 @@
       <c r="I71" s="6"/>
       <c r="J71" s="6"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" ht="15.75" customHeight="1" spans="1:10">
       <c r="A72" s="7"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -5329,7 +6107,7 @@
       <c r="I72" s="6"/>
       <c r="J72" s="6"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" ht="15.75" customHeight="1" spans="1:10">
       <c r="A73" s="7"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -5341,7 +6119,7 @@
       <c r="I73" s="6"/>
       <c r="J73" s="6"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" ht="15.75" customHeight="1" spans="1:10">
       <c r="A74" s="7"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -5353,7 +6131,7 @@
       <c r="I74" s="6"/>
       <c r="J74" s="6"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" ht="15.75" customHeight="1" spans="1:10">
       <c r="A75" s="7"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -5365,7 +6143,7 @@
       <c r="I75" s="6"/>
       <c r="J75" s="6"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" ht="15.75" customHeight="1" spans="1:10">
       <c r="A76" s="7"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -5377,7 +6155,7 @@
       <c r="I76" s="6"/>
       <c r="J76" s="6"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" ht="15.75" customHeight="1" spans="1:10">
       <c r="A77" s="7"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -5389,7 +6167,7 @@
       <c r="I77" s="6"/>
       <c r="J77" s="6"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" ht="15.75" customHeight="1" spans="1:10">
       <c r="A78" s="7"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -5401,7 +6179,7 @@
       <c r="I78" s="6"/>
       <c r="J78" s="6"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" ht="15.75" customHeight="1" spans="1:10">
       <c r="A79" s="7"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -5413,7 +6191,7 @@
       <c r="I79" s="6"/>
       <c r="J79" s="6"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" ht="15.75" customHeight="1" spans="1:10">
       <c r="A80" s="7"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -5425,7 +6203,7 @@
       <c r="I80" s="6"/>
       <c r="J80" s="6"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" ht="15.75" customHeight="1" spans="1:10">
       <c r="A81" s="7"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -5437,7 +6215,7 @@
       <c r="I81" s="6"/>
       <c r="J81" s="6"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" ht="15.75" customHeight="1" spans="1:10">
       <c r="A82" s="7"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -5449,7 +6227,7 @@
       <c r="I82" s="6"/>
       <c r="J82" s="6"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" ht="15.75" customHeight="1" spans="1:10">
       <c r="A83" s="7"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -5461,7 +6239,7 @@
       <c r="I83" s="6"/>
       <c r="J83" s="6"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" ht="15.75" customHeight="1" spans="1:10">
       <c r="A84" s="7"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -5473,7 +6251,7 @@
       <c r="I84" s="6"/>
       <c r="J84" s="6"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" ht="15.75" customHeight="1" spans="1:10">
       <c r="A85" s="7"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -5485,7 +6263,7 @@
       <c r="I85" s="6"/>
       <c r="J85" s="6"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" ht="15.75" customHeight="1" spans="1:10">
       <c r="A86" s="7"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -5497,7 +6275,7 @@
       <c r="I86" s="6"/>
       <c r="J86" s="6"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" ht="15.75" customHeight="1" spans="1:10">
       <c r="A87" s="7"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -5509,7 +6287,7 @@
       <c r="I87" s="6"/>
       <c r="J87" s="6"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" ht="15.75" customHeight="1" spans="1:10">
       <c r="A88" s="7"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -5521,7 +6299,7 @@
       <c r="I88" s="6"/>
       <c r="J88" s="6"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" ht="15.75" customHeight="1" spans="1:10">
       <c r="A89" s="7"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -5533,7 +6311,7 @@
       <c r="I89" s="6"/>
       <c r="J89" s="6"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" ht="15.75" customHeight="1" spans="1:10">
       <c r="A90" s="7"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -5545,7 +6323,7 @@
       <c r="I90" s="6"/>
       <c r="J90" s="6"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" ht="15.75" customHeight="1" spans="1:10">
       <c r="A91" s="7"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -5557,7 +6335,7 @@
       <c r="I91" s="6"/>
       <c r="J91" s="6"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" ht="15.75" customHeight="1" spans="1:10">
       <c r="A92" s="7"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -5569,7 +6347,7 @@
       <c r="I92" s="6"/>
       <c r="J92" s="6"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" ht="15.75" customHeight="1" spans="1:10">
       <c r="A93" s="7"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -5581,7 +6359,7 @@
       <c r="I93" s="6"/>
       <c r="J93" s="6"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" ht="15.75" customHeight="1" spans="1:10">
       <c r="A94" s="7"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -5593,7 +6371,7 @@
       <c r="I94" s="6"/>
       <c r="J94" s="6"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" ht="15.75" customHeight="1" spans="1:10">
       <c r="A95" s="7"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -5605,7 +6383,7 @@
       <c r="I95" s="6"/>
       <c r="J95" s="6"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" ht="15.75" customHeight="1" spans="1:10">
       <c r="A96" s="7"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -5617,7 +6395,7 @@
       <c r="I96" s="6"/>
       <c r="J96" s="6"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" ht="15.75" customHeight="1" spans="1:10">
       <c r="A97" s="7"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -5629,7 +6407,7 @@
       <c r="I97" s="6"/>
       <c r="J97" s="6"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" ht="15.75" customHeight="1" spans="1:10">
       <c r="A98" s="7"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -5641,7 +6419,7 @@
       <c r="I98" s="6"/>
       <c r="J98" s="6"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" ht="15.75" customHeight="1" spans="1:10">
       <c r="A99" s="7"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -5653,7 +6431,7 @@
       <c r="I99" s="6"/>
       <c r="J99" s="6"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" ht="15.75" customHeight="1" spans="1:10">
       <c r="A100" s="7"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -5665,7 +6443,7 @@
       <c r="I100" s="6"/>
       <c r="J100" s="6"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" ht="15.75" customHeight="1" spans="1:10">
       <c r="A101" s="7"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -5677,7 +6455,7 @@
       <c r="I101" s="6"/>
       <c r="J101" s="6"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" ht="15.75" customHeight="1" spans="1:10">
       <c r="A102" s="7"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
@@ -5689,7 +6467,7 @@
       <c r="I102" s="6"/>
       <c r="J102" s="6"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" ht="15.75" customHeight="1" spans="1:10">
       <c r="A103" s="7"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
@@ -5701,7 +6479,7 @@
       <c r="I103" s="6"/>
       <c r="J103" s="6"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" ht="15.75" customHeight="1" spans="1:10">
       <c r="A104" s="7"/>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
@@ -5713,7 +6491,7 @@
       <c r="I104" s="6"/>
       <c r="J104" s="6"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" ht="15.75" customHeight="1" spans="1:10">
       <c r="A105" s="7"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
@@ -5725,7 +6503,7 @@
       <c r="I105" s="6"/>
       <c r="J105" s="6"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" ht="15.75" customHeight="1" spans="1:10">
       <c r="A106" s="7"/>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
@@ -5737,7 +6515,7 @@
       <c r="I106" s="6"/>
       <c r="J106" s="6"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" ht="15.75" customHeight="1" spans="1:10">
       <c r="A107" s="7"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
@@ -5749,7 +6527,7 @@
       <c r="I107" s="6"/>
       <c r="J107" s="6"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" ht="15.75" customHeight="1" spans="1:10">
       <c r="A108" s="7"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
@@ -5761,7 +6539,7 @@
       <c r="I108" s="6"/>
       <c r="J108" s="6"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" ht="15.75" customHeight="1" spans="1:10">
       <c r="A109" s="7"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
@@ -5773,7 +6551,7 @@
       <c r="I109" s="6"/>
       <c r="J109" s="6"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" ht="15.75" customHeight="1" spans="1:10">
       <c r="A110" s="7"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
@@ -5785,7 +6563,7 @@
       <c r="I110" s="6"/>
       <c r="J110" s="6"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" ht="15.75" customHeight="1" spans="1:10">
       <c r="A111" s="7"/>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
@@ -5797,7 +6575,7 @@
       <c r="I111" s="6"/>
       <c r="J111" s="6"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" ht="15.75" customHeight="1" spans="1:10">
       <c r="A112" s="7"/>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
@@ -5809,7 +6587,7 @@
       <c r="I112" s="6"/>
       <c r="J112" s="6"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" ht="15.75" customHeight="1" spans="1:10">
       <c r="A113" s="7"/>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
@@ -5821,7 +6599,7 @@
       <c r="I113" s="6"/>
       <c r="J113" s="6"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" ht="15.75" customHeight="1" spans="1:10">
       <c r="A114" s="7"/>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
@@ -5833,7 +6611,7 @@
       <c r="I114" s="6"/>
       <c r="J114" s="6"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" ht="15.75" customHeight="1" spans="1:10">
       <c r="A115" s="7"/>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
@@ -5845,7 +6623,7 @@
       <c r="I115" s="6"/>
       <c r="J115" s="6"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" ht="15.75" customHeight="1" spans="1:10">
       <c r="A116" s="7"/>
       <c r="B116" s="6"/>
       <c r="C116" s="6"/>
@@ -5857,7 +6635,7 @@
       <c r="I116" s="6"/>
       <c r="J116" s="6"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" ht="15.75" customHeight="1" spans="1:10">
       <c r="A117" s="7"/>
       <c r="B117" s="6"/>
       <c r="C117" s="6"/>
@@ -5869,7 +6647,7 @@
       <c r="I117" s="6"/>
       <c r="J117" s="6"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" ht="15.75" customHeight="1" spans="1:10">
       <c r="A118" s="7"/>
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
@@ -5881,7 +6659,7 @@
       <c r="I118" s="6"/>
       <c r="J118" s="6"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" ht="15.75" customHeight="1" spans="1:10">
       <c r="A119" s="7"/>
       <c r="B119" s="6"/>
       <c r="C119" s="6"/>
@@ -5893,7 +6671,7 @@
       <c r="I119" s="6"/>
       <c r="J119" s="6"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" ht="15.75" customHeight="1" spans="1:10">
       <c r="A120" s="7"/>
       <c r="B120" s="6"/>
       <c r="C120" s="6"/>
@@ -5905,7 +6683,7 @@
       <c r="I120" s="6"/>
       <c r="J120" s="6"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" ht="15.75" customHeight="1" spans="1:10">
       <c r="A121" s="7"/>
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
@@ -5917,7 +6695,7 @@
       <c r="I121" s="6"/>
       <c r="J121" s="6"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" ht="15.75" customHeight="1" spans="1:10">
       <c r="A122" s="7"/>
       <c r="B122" s="6"/>
       <c r="C122" s="6"/>
@@ -5929,7 +6707,7 @@
       <c r="I122" s="6"/>
       <c r="J122" s="6"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" ht="15.75" customHeight="1" spans="1:10">
       <c r="A123" s="7"/>
       <c r="B123" s="6"/>
       <c r="C123" s="6"/>
@@ -5941,7 +6719,7 @@
       <c r="I123" s="6"/>
       <c r="J123" s="6"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" ht="15.75" customHeight="1" spans="1:10">
       <c r="A124" s="7"/>
       <c r="B124" s="6"/>
       <c r="C124" s="6"/>
@@ -5953,7 +6731,7 @@
       <c r="I124" s="6"/>
       <c r="J124" s="6"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" ht="15.75" customHeight="1" spans="1:10">
       <c r="A125" s="7"/>
       <c r="B125" s="6"/>
       <c r="C125" s="6"/>
@@ -5965,7 +6743,7 @@
       <c r="I125" s="6"/>
       <c r="J125" s="6"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" ht="15.75" customHeight="1" spans="1:10">
       <c r="A126" s="7"/>
       <c r="B126" s="6"/>
       <c r="C126" s="6"/>
@@ -5977,7 +6755,7 @@
       <c r="I126" s="6"/>
       <c r="J126" s="6"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" ht="15.75" customHeight="1" spans="1:10">
       <c r="A127" s="7"/>
       <c r="B127" s="6"/>
       <c r="C127" s="6"/>
@@ -5989,7 +6767,7 @@
       <c r="I127" s="6"/>
       <c r="J127" s="6"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" ht="15.75" customHeight="1" spans="1:10">
       <c r="A128" s="7"/>
       <c r="B128" s="6"/>
       <c r="C128" s="6"/>
@@ -6001,7 +6779,7 @@
       <c r="I128" s="6"/>
       <c r="J128" s="6"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" ht="15.75" customHeight="1" spans="1:10">
       <c r="A129" s="7"/>
       <c r="B129" s="6"/>
       <c r="C129" s="6"/>
@@ -6013,7 +6791,7 @@
       <c r="I129" s="6"/>
       <c r="J129" s="6"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" ht="15.75" customHeight="1" spans="1:10">
       <c r="A130" s="7"/>
       <c r="B130" s="6"/>
       <c r="C130" s="6"/>
@@ -6025,7 +6803,7 @@
       <c r="I130" s="6"/>
       <c r="J130" s="6"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" ht="15.75" customHeight="1" spans="1:10">
       <c r="A131" s="7"/>
       <c r="B131" s="6"/>
       <c r="C131" s="6"/>
@@ -6037,7 +6815,7 @@
       <c r="I131" s="6"/>
       <c r="J131" s="6"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" ht="15.75" customHeight="1" spans="1:10">
       <c r="A132" s="7"/>
       <c r="B132" s="6"/>
       <c r="C132" s="6"/>
@@ -6049,7 +6827,7 @@
       <c r="I132" s="6"/>
       <c r="J132" s="6"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" ht="15.75" customHeight="1" spans="1:10">
       <c r="A133" s="7"/>
       <c r="B133" s="6"/>
       <c r="C133" s="6"/>
@@ -6061,7 +6839,7 @@
       <c r="I133" s="6"/>
       <c r="J133" s="6"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" ht="15.75" customHeight="1" spans="1:10">
       <c r="A134" s="7"/>
       <c r="B134" s="6"/>
       <c r="C134" s="6"/>
@@ -6073,7 +6851,7 @@
       <c r="I134" s="6"/>
       <c r="J134" s="6"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" ht="15.75" customHeight="1" spans="1:10">
       <c r="A135" s="7"/>
       <c r="B135" s="6"/>
       <c r="C135" s="6"/>
@@ -6085,7 +6863,7 @@
       <c r="I135" s="6"/>
       <c r="J135" s="6"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" ht="15.75" customHeight="1" spans="1:10">
       <c r="A136" s="7"/>
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
@@ -6097,7 +6875,7 @@
       <c r="I136" s="6"/>
       <c r="J136" s="6"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" ht="15.75" customHeight="1" spans="1:10">
       <c r="A137" s="7"/>
       <c r="B137" s="6"/>
       <c r="C137" s="6"/>
@@ -6109,7 +6887,7 @@
       <c r="I137" s="6"/>
       <c r="J137" s="6"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" ht="15.75" customHeight="1" spans="1:10">
       <c r="A138" s="7"/>
       <c r="B138" s="6"/>
       <c r="C138" s="6"/>
@@ -6121,7 +6899,7 @@
       <c r="I138" s="6"/>
       <c r="J138" s="6"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" ht="15.75" customHeight="1" spans="1:10">
       <c r="A139" s="7"/>
       <c r="B139" s="6"/>
       <c r="C139" s="6"/>
@@ -6133,7 +6911,7 @@
       <c r="I139" s="6"/>
       <c r="J139" s="6"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" ht="15.75" customHeight="1" spans="1:10">
       <c r="A140" s="7"/>
       <c r="B140" s="6"/>
       <c r="C140" s="6"/>
@@ -6145,7 +6923,7 @@
       <c r="I140" s="6"/>
       <c r="J140" s="6"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" ht="15.75" customHeight="1" spans="1:10">
       <c r="A141" s="7"/>
       <c r="B141" s="6"/>
       <c r="C141" s="6"/>
@@ -6157,7 +6935,7 @@
       <c r="I141" s="6"/>
       <c r="J141" s="6"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" ht="15.75" customHeight="1" spans="1:10">
       <c r="A142" s="7"/>
       <c r="B142" s="6"/>
       <c r="C142" s="6"/>
@@ -6169,7 +6947,7 @@
       <c r="I142" s="6"/>
       <c r="J142" s="6"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" ht="15.75" customHeight="1" spans="1:10">
       <c r="A143" s="7"/>
       <c r="B143" s="6"/>
       <c r="C143" s="6"/>
@@ -6181,7 +6959,7 @@
       <c r="I143" s="6"/>
       <c r="J143" s="6"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" ht="15.75" customHeight="1" spans="1:10">
       <c r="A144" s="7"/>
       <c r="B144" s="6"/>
       <c r="C144" s="6"/>
@@ -6193,7 +6971,7 @@
       <c r="I144" s="6"/>
       <c r="J144" s="6"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" ht="15.75" customHeight="1" spans="1:10">
       <c r="A145" s="7"/>
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
@@ -6205,7 +6983,7 @@
       <c r="I145" s="6"/>
       <c r="J145" s="6"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" ht="15.75" customHeight="1" spans="1:10">
       <c r="A146" s="7"/>
       <c r="B146" s="6"/>
       <c r="C146" s="6"/>
@@ -6217,7 +6995,7 @@
       <c r="I146" s="6"/>
       <c r="J146" s="6"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" ht="15.75" customHeight="1" spans="1:10">
       <c r="A147" s="7"/>
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
@@ -6229,7 +7007,7 @@
       <c r="I147" s="6"/>
       <c r="J147" s="6"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" ht="15.75" customHeight="1" spans="1:10">
       <c r="A148" s="7"/>
       <c r="B148" s="6"/>
       <c r="C148" s="6"/>
@@ -6241,7 +7019,7 @@
       <c r="I148" s="6"/>
       <c r="J148" s="6"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" ht="15.75" customHeight="1" spans="1:10">
       <c r="A149" s="7"/>
       <c r="B149" s="6"/>
       <c r="C149" s="6"/>
@@ -6253,7 +7031,7 @@
       <c r="I149" s="6"/>
       <c r="J149" s="6"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" ht="15.75" customHeight="1" spans="1:10">
       <c r="A150" s="7"/>
       <c r="B150" s="6"/>
       <c r="C150" s="6"/>
@@ -6265,7 +7043,7 @@
       <c r="I150" s="6"/>
       <c r="J150" s="6"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" ht="15.75" customHeight="1" spans="1:10">
       <c r="A151" s="7"/>
       <c r="B151" s="6"/>
       <c r="C151" s="6"/>
@@ -6277,7 +7055,7 @@
       <c r="I151" s="6"/>
       <c r="J151" s="6"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" ht="15.75" customHeight="1" spans="1:10">
       <c r="A152" s="7"/>
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
@@ -6289,7 +7067,7 @@
       <c r="I152" s="6"/>
       <c r="J152" s="6"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" ht="15.75" customHeight="1" spans="1:10">
       <c r="A153" s="7"/>
       <c r="B153" s="6"/>
       <c r="C153" s="6"/>
@@ -6301,7 +7079,7 @@
       <c r="I153" s="6"/>
       <c r="J153" s="6"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" ht="15.75" customHeight="1" spans="1:10">
       <c r="A154" s="7"/>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
@@ -6313,7 +7091,7 @@
       <c r="I154" s="6"/>
       <c r="J154" s="6"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" ht="15.75" customHeight="1" spans="1:10">
       <c r="A155" s="7"/>
       <c r="B155" s="6"/>
       <c r="C155" s="6"/>
@@ -6325,7 +7103,7 @@
       <c r="I155" s="6"/>
       <c r="J155" s="6"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" ht="15.75" customHeight="1" spans="1:10">
       <c r="A156" s="7"/>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
@@ -6337,7 +7115,7 @@
       <c r="I156" s="6"/>
       <c r="J156" s="6"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" ht="15.75" customHeight="1" spans="1:10">
       <c r="A157" s="7"/>
       <c r="B157" s="6"/>
       <c r="C157" s="6"/>
@@ -6349,7 +7127,7 @@
       <c r="I157" s="6"/>
       <c r="J157" s="6"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" ht="15.75" customHeight="1" spans="1:10">
       <c r="A158" s="7"/>
       <c r="B158" s="6"/>
       <c r="C158" s="6"/>
@@ -6361,7 +7139,7 @@
       <c r="I158" s="6"/>
       <c r="J158" s="6"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" ht="15.75" customHeight="1" spans="1:10">
       <c r="A159" s="7"/>
       <c r="B159" s="6"/>
       <c r="C159" s="6"/>
@@ -6373,7 +7151,7 @@
       <c r="I159" s="6"/>
       <c r="J159" s="6"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" ht="15.75" customHeight="1" spans="1:10">
       <c r="A160" s="7"/>
       <c r="B160" s="6"/>
       <c r="C160" s="6"/>
@@ -6385,7 +7163,7 @@
       <c r="I160" s="6"/>
       <c r="J160" s="6"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" ht="15.75" customHeight="1" spans="1:10">
       <c r="A161" s="7"/>
       <c r="B161" s="6"/>
       <c r="C161" s="6"/>
@@ -6397,7 +7175,7 @@
       <c r="I161" s="6"/>
       <c r="J161" s="6"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" ht="15.75" customHeight="1" spans="1:10">
       <c r="A162" s="7"/>
       <c r="B162" s="6"/>
       <c r="C162" s="6"/>
@@ -6409,7 +7187,7 @@
       <c r="I162" s="6"/>
       <c r="J162" s="6"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" ht="15.75" customHeight="1" spans="1:10">
       <c r="A163" s="7"/>
       <c r="B163" s="6"/>
       <c r="C163" s="6"/>
@@ -6421,7 +7199,7 @@
       <c r="I163" s="6"/>
       <c r="J163" s="6"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" ht="15.75" customHeight="1" spans="1:10">
       <c r="A164" s="7"/>
       <c r="B164" s="6"/>
       <c r="C164" s="6"/>
@@ -6433,7 +7211,7 @@
       <c r="I164" s="6"/>
       <c r="J164" s="6"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" ht="15.75" customHeight="1" spans="1:10">
       <c r="A165" s="7"/>
       <c r="B165" s="6"/>
       <c r="C165" s="6"/>
@@ -6445,7 +7223,7 @@
       <c r="I165" s="6"/>
       <c r="J165" s="6"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" ht="15.75" customHeight="1" spans="1:10">
       <c r="A166" s="7"/>
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
@@ -6457,7 +7235,7 @@
       <c r="I166" s="6"/>
       <c r="J166" s="6"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" ht="15.75" customHeight="1" spans="1:10">
       <c r="A167" s="7"/>
       <c r="B167" s="6"/>
       <c r="C167" s="6"/>
@@ -6469,7 +7247,7 @@
       <c r="I167" s="6"/>
       <c r="J167" s="6"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" ht="15.75" customHeight="1" spans="1:10">
       <c r="A168" s="7"/>
       <c r="B168" s="6"/>
       <c r="C168" s="6"/>
@@ -6481,7 +7259,7 @@
       <c r="I168" s="6"/>
       <c r="J168" s="6"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" ht="15.75" customHeight="1" spans="1:10">
       <c r="A169" s="7"/>
       <c r="B169" s="6"/>
       <c r="C169" s="6"/>
@@ -6493,7 +7271,7 @@
       <c r="I169" s="6"/>
       <c r="J169" s="6"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" ht="15.75" customHeight="1" spans="1:10">
       <c r="A170" s="7"/>
       <c r="B170" s="6"/>
       <c r="C170" s="6"/>
@@ -6505,7 +7283,7 @@
       <c r="I170" s="6"/>
       <c r="J170" s="6"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" ht="15.75" customHeight="1" spans="1:10">
       <c r="A171" s="7"/>
       <c r="B171" s="6"/>
       <c r="C171" s="6"/>
@@ -6517,7 +7295,7 @@
       <c r="I171" s="6"/>
       <c r="J171" s="6"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" ht="15.75" customHeight="1" spans="1:10">
       <c r="A172" s="7"/>
       <c r="B172" s="6"/>
       <c r="C172" s="6"/>
@@ -6529,7 +7307,7 @@
       <c r="I172" s="6"/>
       <c r="J172" s="6"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" ht="15.75" customHeight="1" spans="1:10">
       <c r="A173" s="7"/>
       <c r="B173" s="6"/>
       <c r="C173" s="6"/>
@@ -6541,7 +7319,7 @@
       <c r="I173" s="6"/>
       <c r="J173" s="6"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" ht="15.75" customHeight="1" spans="1:10">
       <c r="A174" s="7"/>
       <c r="B174" s="6"/>
       <c r="C174" s="6"/>
@@ -6553,7 +7331,7 @@
       <c r="I174" s="6"/>
       <c r="J174" s="6"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" ht="15.75" customHeight="1" spans="1:10">
       <c r="A175" s="7"/>
       <c r="B175" s="6"/>
       <c r="C175" s="6"/>
@@ -6565,7 +7343,7 @@
       <c r="I175" s="6"/>
       <c r="J175" s="6"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" ht="15.75" customHeight="1" spans="1:10">
       <c r="A176" s="7"/>
       <c r="B176" s="6"/>
       <c r="C176" s="6"/>
@@ -6577,7 +7355,7 @@
       <c r="I176" s="6"/>
       <c r="J176" s="6"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" ht="15.75" customHeight="1" spans="1:10">
       <c r="A177" s="7"/>
       <c r="B177" s="6"/>
       <c r="C177" s="6"/>
@@ -6589,7 +7367,7 @@
       <c r="I177" s="6"/>
       <c r="J177" s="6"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" ht="15.75" customHeight="1" spans="1:10">
       <c r="A178" s="7"/>
       <c r="B178" s="6"/>
       <c r="C178" s="6"/>
@@ -6601,7 +7379,7 @@
       <c r="I178" s="6"/>
       <c r="J178" s="6"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" ht="15.75" customHeight="1" spans="1:10">
       <c r="A179" s="7"/>
       <c r="B179" s="6"/>
       <c r="C179" s="6"/>
@@ -6613,7 +7391,7 @@
       <c r="I179" s="6"/>
       <c r="J179" s="6"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" ht="15.75" customHeight="1" spans="1:10">
       <c r="A180" s="7"/>
       <c r="B180" s="6"/>
       <c r="C180" s="6"/>
@@ -6625,7 +7403,7 @@
       <c r="I180" s="6"/>
       <c r="J180" s="6"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" ht="15.75" customHeight="1" spans="1:10">
       <c r="A181" s="7"/>
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
@@ -6637,7 +7415,7 @@
       <c r="I181" s="6"/>
       <c r="J181" s="6"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" ht="15.75" customHeight="1" spans="1:10">
       <c r="A182" s="7"/>
       <c r="B182" s="6"/>
       <c r="C182" s="6"/>
@@ -6649,7 +7427,7 @@
       <c r="I182" s="6"/>
       <c r="J182" s="6"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" ht="15.75" customHeight="1" spans="1:10">
       <c r="A183" s="7"/>
       <c r="B183" s="6"/>
       <c r="C183" s="6"/>
@@ -6661,7 +7439,7 @@
       <c r="I183" s="6"/>
       <c r="J183" s="6"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" ht="15.75" customHeight="1" spans="1:10">
       <c r="A184" s="7"/>
       <c r="B184" s="6"/>
       <c r="C184" s="6"/>
@@ -6673,7 +7451,7 @@
       <c r="I184" s="6"/>
       <c r="J184" s="6"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" ht="15.75" customHeight="1" spans="1:10">
       <c r="A185" s="7"/>
       <c r="B185" s="6"/>
       <c r="C185" s="6"/>
@@ -6685,7 +7463,7 @@
       <c r="I185" s="6"/>
       <c r="J185" s="6"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" ht="15.75" customHeight="1" spans="1:10">
       <c r="A186" s="7"/>
       <c r="B186" s="6"/>
       <c r="C186" s="6"/>
@@ -6697,7 +7475,7 @@
       <c r="I186" s="6"/>
       <c r="J186" s="6"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" ht="15.75" customHeight="1" spans="1:10">
       <c r="A187" s="7"/>
       <c r="B187" s="6"/>
       <c r="C187" s="6"/>
@@ -6709,7 +7487,7 @@
       <c r="I187" s="6"/>
       <c r="J187" s="6"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" ht="15.75" customHeight="1" spans="1:10">
       <c r="A188" s="7"/>
       <c r="B188" s="6"/>
       <c r="C188" s="6"/>
@@ -6721,7 +7499,7 @@
       <c r="I188" s="6"/>
       <c r="J188" s="6"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" ht="15.75" customHeight="1" spans="1:10">
       <c r="A189" s="7"/>
       <c r="B189" s="6"/>
       <c r="C189" s="6"/>
@@ -6733,7 +7511,7 @@
       <c r="I189" s="6"/>
       <c r="J189" s="6"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" ht="15.75" customHeight="1" spans="1:10">
       <c r="A190" s="7"/>
       <c r="B190" s="6"/>
       <c r="C190" s="6"/>
@@ -6745,7 +7523,7 @@
       <c r="I190" s="6"/>
       <c r="J190" s="6"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" ht="15.75" customHeight="1" spans="1:10">
       <c r="A191" s="7"/>
       <c r="B191" s="6"/>
       <c r="C191" s="6"/>
@@ -6757,7 +7535,7 @@
       <c r="I191" s="6"/>
       <c r="J191" s="6"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" ht="15.75" customHeight="1" spans="1:10">
       <c r="A192" s="7"/>
       <c r="B192" s="6"/>
       <c r="C192" s="6"/>
@@ -6769,7 +7547,7 @@
       <c r="I192" s="6"/>
       <c r="J192" s="6"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" ht="15.75" customHeight="1" spans="1:10">
       <c r="A193" s="7"/>
       <c r="B193" s="6"/>
       <c r="C193" s="6"/>
@@ -6781,7 +7559,7 @@
       <c r="I193" s="6"/>
       <c r="J193" s="6"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" ht="15.75" customHeight="1" spans="1:10">
       <c r="A194" s="7"/>
       <c r="B194" s="6"/>
       <c r="C194" s="6"/>
@@ -6793,7 +7571,7 @@
       <c r="I194" s="6"/>
       <c r="J194" s="6"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" ht="15.75" customHeight="1" spans="1:10">
       <c r="A195" s="7"/>
       <c r="B195" s="6"/>
       <c r="C195" s="6"/>
@@ -6805,7 +7583,7 @@
       <c r="I195" s="6"/>
       <c r="J195" s="6"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" ht="15.75" customHeight="1" spans="1:10">
       <c r="A196" s="7"/>
       <c r="B196" s="6"/>
       <c r="C196" s="6"/>
@@ -6817,7 +7595,7 @@
       <c r="I196" s="6"/>
       <c r="J196" s="6"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" ht="15.75" customHeight="1" spans="1:10">
       <c r="A197" s="7"/>
       <c r="B197" s="6"/>
       <c r="C197" s="6"/>
@@ -6829,7 +7607,7 @@
       <c r="I197" s="6"/>
       <c r="J197" s="6"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" ht="15.75" customHeight="1" spans="1:10">
       <c r="A198" s="7"/>
       <c r="B198" s="6"/>
       <c r="C198" s="6"/>
@@ -6841,7 +7619,7 @@
       <c r="I198" s="6"/>
       <c r="J198" s="6"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" ht="15.75" customHeight="1" spans="1:10">
       <c r="A199" s="7"/>
       <c r="B199" s="6"/>
       <c r="C199" s="6"/>
@@ -6853,7 +7631,7 @@
       <c r="I199" s="6"/>
       <c r="J199" s="6"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" ht="15.75" customHeight="1" spans="1:10">
       <c r="A200" s="7"/>
       <c r="B200" s="6"/>
       <c r="C200" s="6"/>
@@ -6865,7 +7643,7 @@
       <c r="I200" s="6"/>
       <c r="J200" s="6"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" ht="15.75" customHeight="1" spans="1:10">
       <c r="A201" s="7"/>
       <c r="B201" s="6"/>
       <c r="C201" s="6"/>
@@ -6877,7 +7655,7 @@
       <c r="I201" s="6"/>
       <c r="J201" s="6"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" ht="15.75" customHeight="1" spans="1:10">
       <c r="A202" s="7"/>
       <c r="B202" s="6"/>
       <c r="C202" s="6"/>
@@ -6889,7 +7667,7 @@
       <c r="I202" s="6"/>
       <c r="J202" s="6"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" ht="15.75" customHeight="1" spans="1:10">
       <c r="A203" s="7"/>
       <c r="B203" s="6"/>
       <c r="C203" s="6"/>
@@ -6901,7 +7679,7 @@
       <c r="I203" s="6"/>
       <c r="J203" s="6"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" ht="15.75" customHeight="1" spans="1:10">
       <c r="A204" s="7"/>
       <c r="B204" s="6"/>
       <c r="C204" s="6"/>
@@ -6913,7 +7691,7 @@
       <c r="I204" s="6"/>
       <c r="J204" s="6"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" ht="15.75" customHeight="1" spans="1:10">
       <c r="A205" s="7"/>
       <c r="B205" s="6"/>
       <c r="C205" s="6"/>
@@ -6925,7 +7703,7 @@
       <c r="I205" s="6"/>
       <c r="J205" s="6"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" ht="15.75" customHeight="1" spans="1:10">
       <c r="A206" s="7"/>
       <c r="B206" s="6"/>
       <c r="C206" s="6"/>
@@ -6937,7 +7715,7 @@
       <c r="I206" s="6"/>
       <c r="J206" s="6"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" ht="15.75" customHeight="1" spans="1:10">
       <c r="A207" s="7"/>
       <c r="B207" s="6"/>
       <c r="C207" s="6"/>
@@ -6949,7 +7727,7 @@
       <c r="I207" s="6"/>
       <c r="J207" s="6"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" ht="15.75" customHeight="1" spans="1:10">
       <c r="A208" s="7"/>
       <c r="B208" s="6"/>
       <c r="C208" s="6"/>
@@ -6961,7 +7739,7 @@
       <c r="I208" s="6"/>
       <c r="J208" s="6"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" ht="15.75" customHeight="1" spans="1:10">
       <c r="A209" s="7"/>
       <c r="B209" s="6"/>
       <c r="C209" s="6"/>
@@ -6973,7 +7751,7 @@
       <c r="I209" s="6"/>
       <c r="J209" s="6"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" ht="15.75" customHeight="1" spans="1:10">
       <c r="A210" s="7"/>
       <c r="B210" s="6"/>
       <c r="C210" s="6"/>
@@ -6985,7 +7763,7 @@
       <c r="I210" s="6"/>
       <c r="J210" s="6"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" ht="15.75" customHeight="1" spans="1:10">
       <c r="A211" s="7"/>
       <c r="B211" s="6"/>
       <c r="C211" s="6"/>
@@ -6997,7 +7775,7 @@
       <c r="I211" s="6"/>
       <c r="J211" s="6"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" ht="15.75" customHeight="1" spans="1:10">
       <c r="A212" s="7"/>
       <c r="B212" s="6"/>
       <c r="C212" s="6"/>
@@ -7009,7 +7787,7 @@
       <c r="I212" s="6"/>
       <c r="J212" s="6"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" ht="15.75" customHeight="1" spans="1:10">
       <c r="A213" s="7"/>
       <c r="B213" s="6"/>
       <c r="C213" s="6"/>
@@ -7021,7 +7799,7 @@
       <c r="I213" s="6"/>
       <c r="J213" s="6"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" ht="15.75" customHeight="1" spans="1:10">
       <c r="A214" s="7"/>
       <c r="B214" s="6"/>
       <c r="C214" s="6"/>
@@ -7033,7 +7811,7 @@
       <c r="I214" s="6"/>
       <c r="J214" s="6"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" ht="15.75" customHeight="1" spans="1:10">
       <c r="A215" s="7"/>
       <c r="B215" s="6"/>
       <c r="C215" s="6"/>
@@ -7045,7 +7823,7 @@
       <c r="I215" s="6"/>
       <c r="J215" s="6"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" ht="15.75" customHeight="1" spans="1:10">
       <c r="A216" s="7"/>
       <c r="B216" s="6"/>
       <c r="C216" s="6"/>
@@ -7057,7 +7835,7 @@
       <c r="I216" s="6"/>
       <c r="J216" s="6"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" ht="15.75" customHeight="1" spans="1:10">
       <c r="A217" s="7"/>
       <c r="B217" s="6"/>
       <c r="C217" s="6"/>
@@ -7069,7 +7847,7 @@
       <c r="I217" s="6"/>
       <c r="J217" s="6"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" ht="15.75" customHeight="1" spans="1:10">
       <c r="A218" s="7"/>
       <c r="B218" s="6"/>
       <c r="C218" s="6"/>
@@ -7081,7 +7859,7 @@
       <c r="I218" s="6"/>
       <c r="J218" s="6"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" ht="15.75" customHeight="1" spans="1:10">
       <c r="A219" s="7"/>
       <c r="B219" s="6"/>
       <c r="C219" s="6"/>
@@ -7093,7 +7871,7 @@
       <c r="I219" s="6"/>
       <c r="J219" s="6"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" ht="15.75" customHeight="1" spans="1:10">
       <c r="A220" s="7"/>
       <c r="B220" s="6"/>
       <c r="C220" s="6"/>
@@ -7105,7 +7883,7 @@
       <c r="I220" s="6"/>
       <c r="J220" s="6"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1">
+    <row r="221" ht="15.75" customHeight="1" spans="1:10">
       <c r="A221" s="7"/>
       <c r="B221" s="7"/>
       <c r="C221" s="7"/>
@@ -7117,7 +7895,7 @@
       <c r="I221" s="7"/>
       <c r="J221" s="7"/>
     </row>
-    <row r="222" ht="15.75" customHeight="1">
+    <row r="222" ht="15.75" customHeight="1" spans="1:10">
       <c r="A222" s="7"/>
       <c r="B222" s="7"/>
       <c r="C222" s="7"/>
@@ -7129,7 +7907,7 @@
       <c r="I222" s="7"/>
       <c r="J222" s="7"/>
     </row>
-    <row r="223" ht="15.75" customHeight="1">
+    <row r="223" ht="15.75" customHeight="1" spans="1:10">
       <c r="A223" s="7"/>
       <c r="B223" s="7"/>
       <c r="C223" s="7"/>
@@ -7141,7 +7919,7 @@
       <c r="I223" s="7"/>
       <c r="J223" s="7"/>
     </row>
-    <row r="224" ht="15.75" customHeight="1">
+    <row r="224" ht="15.75" customHeight="1" spans="1:10">
       <c r="A224" s="7"/>
       <c r="B224" s="7"/>
       <c r="C224" s="7"/>
@@ -7153,7 +7931,7 @@
       <c r="I224" s="7"/>
       <c r="J224" s="7"/>
     </row>
-    <row r="225" ht="15.75" customHeight="1">
+    <row r="225" ht="15.75" customHeight="1" spans="1:10">
       <c r="A225" s="7"/>
       <c r="B225" s="7"/>
       <c r="C225" s="7"/>
@@ -7165,7 +7943,7 @@
       <c r="I225" s="7"/>
       <c r="J225" s="7"/>
     </row>
-    <row r="226" ht="15.75" customHeight="1">
+    <row r="226" ht="15.75" customHeight="1" spans="1:10">
       <c r="A226" s="7"/>
       <c r="B226" s="7"/>
       <c r="C226" s="7"/>
@@ -7177,7 +7955,7 @@
       <c r="I226" s="7"/>
       <c r="J226" s="7"/>
     </row>
-    <row r="227" ht="15.75" customHeight="1">
+    <row r="227" ht="15.75" customHeight="1" spans="1:10">
       <c r="A227" s="7"/>
       <c r="B227" s="7"/>
       <c r="C227" s="7"/>
@@ -7189,7 +7967,7 @@
       <c r="I227" s="7"/>
       <c r="J227" s="7"/>
     </row>
-    <row r="228" ht="15.75" customHeight="1">
+    <row r="228" ht="15.75" customHeight="1" spans="1:10">
       <c r="A228" s="7"/>
       <c r="B228" s="7"/>
       <c r="C228" s="7"/>
@@ -7201,7 +7979,7 @@
       <c r="I228" s="7"/>
       <c r="J228" s="7"/>
     </row>
-    <row r="229" ht="15.75" customHeight="1">
+    <row r="229" ht="15.75" customHeight="1" spans="1:10">
       <c r="A229" s="7"/>
       <c r="B229" s="7"/>
       <c r="C229" s="7"/>
@@ -7213,7 +7991,7 @@
       <c r="I229" s="7"/>
       <c r="J229" s="7"/>
     </row>
-    <row r="230" ht="15.75" customHeight="1">
+    <row r="230" ht="15.75" customHeight="1" spans="1:10">
       <c r="A230" s="7"/>
       <c r="B230" s="7"/>
       <c r="C230" s="7"/>
@@ -7225,7 +8003,7 @@
       <c r="I230" s="7"/>
       <c r="J230" s="7"/>
     </row>
-    <row r="231" ht="15.75" customHeight="1">
+    <row r="231" ht="15.75" customHeight="1" spans="1:10">
       <c r="A231" s="7"/>
       <c r="B231" s="7"/>
       <c r="C231" s="7"/>
@@ -7237,7 +8015,7 @@
       <c r="I231" s="7"/>
       <c r="J231" s="7"/>
     </row>
-    <row r="232" ht="15.75" customHeight="1">
+    <row r="232" ht="15.75" customHeight="1" spans="1:10">
       <c r="A232" s="7"/>
       <c r="B232" s="7"/>
       <c r="C232" s="7"/>
@@ -8018,17 +8796,13 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="4">
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="F27:J27"/>
-    <mergeCell ref="I28:J31"/>
-    <mergeCell ref="A32:A33"/>
     <mergeCell ref="C32:E32"/>
     <mergeCell ref="F32:J32"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>